--- a/demo/coaching-skool/demo-member-sheet.xlsx
+++ b/demo/coaching-skool/demo-member-sheet.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q994"/>
+  <dimension ref="A1:T994"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="26" customWidth="1" style="18" min="1" max="1"/>
@@ -541,6 +541,21 @@
           <t>skip</t>
         </is>
       </c>
+      <c r="R1" s="19" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="S1" s="19" t="inlineStr">
+        <is>
+          <t>posts</t>
+        </is>
+      </c>
+      <c r="T1" s="19" t="inlineStr">
+        <is>
+          <t>intro_posted</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
@@ -589,6 +604,19 @@
       <c r="M2" s="0" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>owen.fontaine@example.com</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>29</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -637,6 +665,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>tomas.grimshaw@example.com</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>36</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -683,6 +724,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>terrence.vanderbilt@example.com</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>30</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -729,6 +783,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>niklas.voss@example.com</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>29</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -775,6 +842,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>quentin.wycliffe@example.com</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>33</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -821,6 +901,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>vernon.bramwell@example.com</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>38</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -867,6 +960,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>basil.whitfield@example.com</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>13</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -913,6 +1019,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>xavier.yates@example.com</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>12</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -965,6 +1084,19 @@
       <c r="M10" s="0" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>franklin.hawthorne@example.com</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>33</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1013,6 +1145,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>gavin.mumford@example.com</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>31</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -1059,6 +1204,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>luigi.northgate@example.com</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>40</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -1105,6 +1263,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>peter.sanderson@example.com</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>12</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -1151,6 +1322,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>julius.yates@example.com</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -1197,6 +1381,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>hamish.lindqvist@example.com</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>29</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="18">
       <c r="A16" s="9" t="inlineStr">
@@ -1243,6 +1440,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>silas.quigley@example.com</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="18">
       <c r="A17" s="9" t="inlineStr">
@@ -1289,6 +1499,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>padraig.fairbanks@example.com</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="18">
       <c r="A18" s="9" t="inlineStr">
@@ -1337,6 +1560,19 @@
       <c r="M18" s="0" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>franklin.yarrow@example.com</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1385,6 +1621,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>stanley.pomeroy@example.com</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>35</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="18">
       <c r="A20" s="9" t="inlineStr">
@@ -1431,6 +1680,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>caleb.ashford@example.com</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="18">
       <c r="A21" s="9" t="inlineStr">
@@ -1477,6 +1739,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>derek.larimore@example.com</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>39</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="18">
       <c r="A22" s="9" t="inlineStr">
@@ -1523,6 +1798,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>enzo.ingram@example.com</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>26</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="18">
       <c r="A23" s="9" t="inlineStr">
@@ -1569,6 +1857,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>andrei.upton@example.com</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>29</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="18">
       <c r="A24" s="9" t="inlineStr">
@@ -1615,6 +1916,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>anders.zeigler@example.com</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>40</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="18">
       <c r="A25" s="9" t="inlineStr">
@@ -1663,6 +1977,19 @@
       <c r="M25" s="0" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>duncan.jamison@example.com</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>11</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1711,6 +2038,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>karl.rowntree@example.com</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>40</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="18">
       <c r="A27" s="9" t="inlineStr">
@@ -1757,6 +2097,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>micah.yardley@example.com</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="18">
       <c r="A28" s="9" t="inlineStr">
@@ -1803,6 +2156,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>rafael.huxley@example.com</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>34</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="18">
       <c r="A29" s="9" t="inlineStr">
@@ -1849,6 +2215,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>xavier.jernigan@example.com</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="18">
       <c r="A30" s="9" t="inlineStr">
@@ -1895,6 +2274,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>luigi.winslow@example.com</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="18">
       <c r="A31" s="9" t="inlineStr">
@@ -1941,6 +2333,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>rowan.ridgeway@example.com</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="18">
       <c r="A32" s="9" t="inlineStr">
@@ -1987,6 +2392,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>silas.ingram@example.com</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>13</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="18">
       <c r="A33" s="9" t="inlineStr">
@@ -2033,6 +2451,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>lars.glendower@example.com</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>16</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="18">
       <c r="A34" s="9" t="inlineStr">
@@ -2081,6 +2512,19 @@
       <c r="M34" s="0" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>terrence.lachlan@example.com</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>39</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -2129,6 +2573,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>ivan.montgomery@example.com</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="18">
       <c r="A36" s="9" t="inlineStr">
@@ -2175,6 +2632,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>xavier.ashford@example.com</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>30</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="18">
       <c r="A37" s="9" t="inlineStr">
@@ -2221,6 +2691,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>mateo.calloway@example.com</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>21</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="18">
       <c r="A38" s="9" t="inlineStr">
@@ -2267,6 +2750,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>peter.jamison@example.com</t>
+        </is>
+      </c>
+      <c r="S38" t="n">
+        <v>29</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="18">
       <c r="A39" s="9" t="inlineStr">
@@ -2313,6 +2809,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>levi.pruitt@example.com</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>38</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="18">
       <c r="A40" s="9" t="inlineStr">
@@ -2361,6 +2870,19 @@
       <c r="M40" s="0" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>padraig.fairview@example.com</t>
+        </is>
+      </c>
+      <c r="S40" t="n">
+        <v>13</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -2409,6 +2931,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>angus.quigley@example.com</t>
+        </is>
+      </c>
+      <c r="S41" t="n">
+        <v>34</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="18">
       <c r="A42" s="9" t="inlineStr">
@@ -2455,6 +2990,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>harold.tavish@example.com</t>
+        </is>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="18">
       <c r="A43" s="9" t="inlineStr">
@@ -2501,6 +3049,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>edmund.grimshaw@example.com</t>
+        </is>
+      </c>
+      <c r="S43" t="n">
+        <v>19</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="18">
       <c r="A44" s="9" t="inlineStr">
@@ -2547,6 +3108,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>callum.dunhill@example.com</t>
+        </is>
+      </c>
+      <c r="S44" t="n">
+        <v>32</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="18">
       <c r="A45" s="9" t="inlineStr">
@@ -2593,6 +3167,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>levi.yardley@example.com</t>
+        </is>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="18">
       <c r="A46" s="9" t="inlineStr">
@@ -2639,6 +3226,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>xavier.ingram@example.com</t>
+        </is>
+      </c>
+      <c r="S46" t="n">
+        <v>6</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="18">
       <c r="A47" s="9" t="inlineStr">
@@ -2685,6 +3285,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>nathaniel.quimby@example.com</t>
+        </is>
+      </c>
+      <c r="S47" t="n">
+        <v>30</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="18">
       <c r="A48" s="9" t="inlineStr">
@@ -2731,6 +3344,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>derek.sinclair@example.com</t>
+        </is>
+      </c>
+      <c r="S48" t="n">
+        <v>18</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="18">
       <c r="A49" s="9" t="inlineStr">
@@ -2777,6 +3403,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>andre.marlowe@example.com</t>
+        </is>
+      </c>
+      <c r="S49" t="n">
+        <v>27</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="18">
       <c r="A50" s="9" t="inlineStr">
@@ -2823,6 +3462,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>clifford.quimby@example.com</t>
+        </is>
+      </c>
+      <c r="S50" t="n">
+        <v>36</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="18">
       <c r="A51" s="9" t="inlineStr">
@@ -2869,6 +3521,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>clifford.eastwood@example.com</t>
+        </is>
+      </c>
+      <c r="S51" t="n">
+        <v>6</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="18">
       <c r="A52" s="9" t="inlineStr">
@@ -2915,6 +3580,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>angus.orchard@example.com</t>
+        </is>
+      </c>
+      <c r="S52" t="n">
+        <v>17</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="18">
       <c r="A53" s="9" t="inlineStr">
@@ -2961,6 +3639,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>stefan.fairview@example.com</t>
+        </is>
+      </c>
+      <c r="S53" t="n">
+        <v>21</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="18">
       <c r="A54" s="9" t="inlineStr">
@@ -3009,6 +3700,19 @@
       <c r="M54" s="0" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>malcolm.corbin@example.com</t>
+        </is>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -3057,6 +3761,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>oscar.fenwick@example.com</t>
+        </is>
+      </c>
+      <c r="S55" t="n">
+        <v>33</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="18">
       <c r="A56" s="9" t="inlineStr">
@@ -3103,6 +3820,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>adam.carmichael@example.com</t>
+        </is>
+      </c>
+      <c r="S56" t="n">
+        <v>19</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="18">
       <c r="A57" s="9" t="inlineStr">
@@ -3149,6 +3879,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>andrei.pruitt@example.com</t>
+        </is>
+      </c>
+      <c r="S57" t="n">
+        <v>2</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="18">
       <c r="A58" s="9" t="inlineStr">
@@ -3195,6 +3938,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>cedric.montgomery@example.com</t>
+        </is>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="18">
       <c r="A59" s="9" t="inlineStr">
@@ -3241,6 +3997,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>jonah.thornbury@example.com</t>
+        </is>
+      </c>
+      <c r="S59" t="n">
+        <v>26</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="18">
       <c r="A60" s="9" t="inlineStr">
@@ -3289,6 +4058,19 @@
       <c r="M60" s="0" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>owen.yandell@example.com</t>
+        </is>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3337,6 +4119,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>colin.zabriskie@example.com</t>
+        </is>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="18">
       <c r="A62" s="9" t="inlineStr">
@@ -3383,6 +4178,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>raymond.elbridge@example.com</t>
+        </is>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="18">
       <c r="A63" s="9" t="inlineStr">
@@ -3429,6 +4237,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>julian.northgate@example.com</t>
+        </is>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="15.75" customHeight="1" s="18">
       <c r="A64" s="9" t="inlineStr">
@@ -3475,6 +4296,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>colin.thornbury@example.com</t>
+        </is>
+      </c>
+      <c r="S64" t="n">
+        <v>4</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="18">
       <c r="A65" s="9" t="inlineStr">
@@ -3521,6 +4355,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>inigo.corbin@example.com</t>
+        </is>
+      </c>
+      <c r="S65" t="n">
+        <v>31</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="18">
       <c r="A66" s="9" t="inlineStr">
@@ -3569,6 +4416,19 @@
       <c r="M66" s="0" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>colin.winterbourne@example.com</t>
+        </is>
+      </c>
+      <c r="S66" t="n">
+        <v>26</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -3617,6 +4477,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>kendrick.kessler@example.com</t>
+        </is>
+      </c>
+      <c r="S67" t="n">
+        <v>37</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="18">
       <c r="A68" s="9" t="inlineStr">
@@ -3663,6 +4536,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>peter.thornbury@example.com</t>
+        </is>
+      </c>
+      <c r="S68" t="n">
+        <v>13</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="18">
       <c r="A69" s="9" t="inlineStr">
@@ -3709,6 +4595,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>emmett.wycliffe@example.com</t>
+        </is>
+      </c>
+      <c r="S69" t="n">
+        <v>18</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="18">
       <c r="A70" s="9" t="inlineStr">
@@ -3755,6 +4654,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>hugo.ridgeway@example.com</t>
+        </is>
+      </c>
+      <c r="S70" t="n">
+        <v>20</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="18">
       <c r="A71" s="9" t="inlineStr">
@@ -3801,6 +4713,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>levi.quimby@example.com</t>
+        </is>
+      </c>
+      <c r="S71" t="n">
+        <v>27</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="18">
       <c r="A72" s="9" t="inlineStr">
@@ -3847,6 +4772,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>hamish.oakeshott@example.com</t>
+        </is>
+      </c>
+      <c r="S72" t="n">
+        <v>8</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="18">
       <c r="A73" s="9" t="inlineStr">
@@ -3893,6 +4831,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>quentin.lindqvist@example.com</t>
+        </is>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="18">
       <c r="A74" s="9" t="inlineStr">
@@ -3941,6 +4892,19 @@
       <c r="M74" s="0" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>wallace.pemberton@example.com</t>
+        </is>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -3989,6 +4953,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>xavier.garrick@example.com</t>
+        </is>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="18">
       <c r="A76" s="9" t="inlineStr">
@@ -4035,6 +5012,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>marco.mowbray@example.com</t>
+        </is>
+      </c>
+      <c r="S76" t="n">
+        <v>12</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="15.75" customHeight="1" s="18">
       <c r="A77" s="9" t="inlineStr">
@@ -4081,6 +5071,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>terrence.islington@example.com</t>
+        </is>
+      </c>
+      <c r="S77" t="n">
+        <v>13</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="15.75" customHeight="1" s="18">
       <c r="A78" s="9" t="inlineStr">
@@ -4127,6 +5130,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>peter.fairview@example.com</t>
+        </is>
+      </c>
+      <c r="S78" t="n">
+        <v>13</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="18">
       <c r="A79" s="9" t="inlineStr">
@@ -4175,6 +5191,19 @@
       <c r="M79" s="0" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>enzo.pomeroy@example.com</t>
+        </is>
+      </c>
+      <c r="S79" t="n">
+        <v>9</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -4223,6 +5252,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>callum.norwood@example.com</t>
+        </is>
+      </c>
+      <c r="S80" t="n">
+        <v>25</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="15.75" customHeight="1" s="18">
       <c r="A81" s="9" t="inlineStr">
@@ -4269,6 +5311,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>tomas.kirkland@example.com</t>
+        </is>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15.75" customHeight="1" s="18">
       <c r="A82" s="9" t="inlineStr">
@@ -4315,6 +5370,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>terrence.quimby@example.com</t>
+        </is>
+      </c>
+      <c r="S82" t="n">
+        <v>14</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="15.75" customHeight="1" s="18">
       <c r="A83" s="9" t="inlineStr">
@@ -4361,6 +5429,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>fraser.islington@example.com</t>
+        </is>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="15.75" customHeight="1" s="18">
       <c r="A84" s="9" t="inlineStr">
@@ -4407,6 +5488,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>julian.quimby@example.com</t>
+        </is>
+      </c>
+      <c r="S84" t="n">
+        <v>38</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="15.75" customHeight="1" s="18">
       <c r="A85" s="9" t="inlineStr">
@@ -4455,6 +5549,19 @@
       <c r="M85" s="0" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>mateo.fairbanks@example.com</t>
+        </is>
+      </c>
+      <c r="S85" t="n">
+        <v>2</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -4503,6 +5610,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>fraser.sanderson@example.com</t>
+        </is>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="15.75" customHeight="1" s="18">
       <c r="A87" s="9" t="inlineStr">
@@ -4549,6 +5669,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>fraser.ironside@example.com</t>
+        </is>
+      </c>
+      <c r="S87" t="n">
+        <v>39</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="15.75" customHeight="1" s="18">
       <c r="A88" s="9" t="inlineStr">
@@ -4595,6 +5728,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>wallace.clayborne@example.com</t>
+        </is>
+      </c>
+      <c r="S88" t="n">
+        <v>37</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="15.75" customHeight="1" s="18">
       <c r="A89" s="9" t="inlineStr">
@@ -4641,6 +5787,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>andre.zeigler@example.com</t>
+        </is>
+      </c>
+      <c r="S89" t="n">
+        <v>7</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="15.75" customHeight="1" s="18">
       <c r="A90" s="9" t="inlineStr">
@@ -4687,6 +5846,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>duncan.ironside@example.com</t>
+        </is>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="15.75" customHeight="1" s="18">
       <c r="A91" s="9" t="inlineStr">
@@ -4733,6 +5905,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>julian.waverly@example.com</t>
+        </is>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="15.75" customHeight="1" s="18">
       <c r="A92" s="9" t="inlineStr">
@@ -4779,6 +5964,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>silas.hawthorne@example.com</t>
+        </is>
+      </c>
+      <c r="S92" t="n">
+        <v>1</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="15.75" customHeight="1" s="18">
       <c r="A93" s="9" t="inlineStr">
@@ -4825,6 +6023,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>nathan.pemberton@example.com</t>
+        </is>
+      </c>
+      <c r="S93" t="n">
+        <v>22</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="15.75" customHeight="1" s="18">
       <c r="A94" s="9" t="inlineStr">
@@ -4871,6 +6082,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>paolo.sanderson@example.com</t>
+        </is>
+      </c>
+      <c r="S94" t="n">
+        <v>19</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="15.75" customHeight="1" s="18">
       <c r="A95" s="9" t="inlineStr">
@@ -4917,6 +6141,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>emmett.sinclair@example.com</t>
+        </is>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="15.75" customHeight="1" s="18">
       <c r="A96" s="9" t="inlineStr">
@@ -4963,6 +6200,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>clifford.cranfield@example.com</t>
+        </is>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="18">
       <c r="A97" s="9" t="inlineStr">
@@ -5009,6 +6259,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>marcus.radcliffe@example.com</t>
+        </is>
+      </c>
+      <c r="S97" t="n">
+        <v>16</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="15.75" customHeight="1" s="18">
       <c r="A98" s="9" t="inlineStr">
@@ -5055,6 +6318,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>franklin.thornbury@example.com</t>
+        </is>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="15.75" customHeight="1" s="18">
       <c r="A99" s="9" t="inlineStr">
@@ -5101,6 +6377,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>leonard.whitfield@example.com</t>
+        </is>
+      </c>
+      <c r="S99" t="n">
+        <v>40</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="18">
       <c r="A100" s="9" t="inlineStr">
@@ -5147,6 +6436,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>rowan.jetley@example.com</t>
+        </is>
+      </c>
+      <c r="S100" t="n">
+        <v>38</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="15.75" customHeight="1" s="18">
       <c r="A101" s="9" t="inlineStr">
@@ -5193,6 +6495,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>julius.jardine@example.com</t>
+        </is>
+      </c>
+      <c r="S101" t="n">
+        <v>37</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="15.75" customHeight="1" s="18">
       <c r="A102" s="9" t="inlineStr">
@@ -5239,6 +6554,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>lars.underhill@example.com</t>
+        </is>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="15.75" customHeight="1" s="18">
       <c r="A103" s="9" t="inlineStr">
@@ -5285,6 +6613,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>nathaniel.lachlan@example.com</t>
+        </is>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="15.75" customHeight="1" s="18">
       <c r="A104" s="9" t="inlineStr">
@@ -5331,6 +6672,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>grant.ridgeway@example.com</t>
+        </is>
+      </c>
+      <c r="S104" t="n">
+        <v>15</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="15.75" customHeight="1" s="18">
       <c r="A105" s="9" t="inlineStr">
@@ -5377,6 +6731,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>tomas.hollingsworth@example.com</t>
+        </is>
+      </c>
+      <c r="S105" t="n">
+        <v>40</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="15.75" customHeight="1" s="18">
       <c r="A106" s="9" t="inlineStr">
@@ -5423,6 +6790,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>silas.fairview@example.com</t>
+        </is>
+      </c>
+      <c r="S106" t="n">
+        <v>13</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="15.75" customHeight="1" s="18">
       <c r="A107" s="9" t="inlineStr">
@@ -5469,6 +6849,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>franklin.orchard@example.com</t>
+        </is>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="15.75" customHeight="1" s="18">
       <c r="A108" s="9" t="inlineStr">
@@ -5515,6 +6908,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>martin.lindqvist@example.com</t>
+        </is>
+      </c>
+      <c r="S108" t="n">
+        <v>36</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="15.75" customHeight="1" s="18">
       <c r="A109" s="9" t="inlineStr">
@@ -5561,6 +6967,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>bruno.rothbury@example.com</t>
+        </is>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="15.75" customHeight="1" s="18">
       <c r="A110" s="9" t="inlineStr">
@@ -5607,6 +7026,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>callum.kelso@example.com</t>
+        </is>
+      </c>
+      <c r="S110" t="n">
+        <v>31</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="15.75" customHeight="1" s="18">
       <c r="A111" s="9" t="inlineStr">
@@ -5653,6 +7085,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>emmett.trenchard@example.com</t>
+        </is>
+      </c>
+      <c r="S111" t="n">
+        <v>27</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="15.75" customHeight="1" s="18">
       <c r="A112" s="9" t="inlineStr">
@@ -5699,6 +7144,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>mateo.yardley@example.com</t>
+        </is>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="15.75" customHeight="1" s="18">
       <c r="A113" s="9" t="inlineStr">
@@ -5745,6 +7203,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>stanley.bramwell@example.com</t>
+        </is>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="15.75" customHeight="1" s="18">
       <c r="A114" s="9" t="inlineStr">
@@ -5791,6 +7262,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>wallace.lindqvist@example.com</t>
+        </is>
+      </c>
+      <c r="S114" t="n">
+        <v>17</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="15.75" customHeight="1" s="18">
       <c r="A115" s="9" t="inlineStr">
@@ -5837,6 +7321,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>paolo.ingram@example.com</t>
+        </is>
+      </c>
+      <c r="S115" t="n">
+        <v>26</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15.75" customHeight="1" s="18">
       <c r="A116" s="9" t="inlineStr">
@@ -5883,6 +7380,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>oscar.selwyn@example.com</t>
+        </is>
+      </c>
+      <c r="S116" t="n">
+        <v>39</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="15.75" customHeight="1" s="18">
       <c r="A117" s="9" t="inlineStr">
@@ -5929,6 +7439,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>ivan.tavish@example.com</t>
+        </is>
+      </c>
+      <c r="S117" t="n">
+        <v>34</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="15.75" customHeight="1" s="18">
       <c r="A118" s="9" t="inlineStr">
@@ -5975,6 +7498,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>declan.halewood@example.com</t>
+        </is>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15.75" customHeight="1" s="18">
       <c r="A119" s="9" t="inlineStr">
@@ -6021,6 +7557,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>vernon.harrington@example.com</t>
+        </is>
+      </c>
+      <c r="S119" t="n">
+        <v>5</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="15.75" customHeight="1" s="18">
       <c r="A120" s="9" t="inlineStr">
@@ -6067,6 +7616,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>leonard.rowntree@example.com</t>
+        </is>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="15.75" customHeight="1" s="18">
       <c r="A121" s="9" t="inlineStr">
@@ -6113,6 +7675,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>alvaro.montgomery@example.com</t>
+        </is>
+      </c>
+      <c r="S121" t="n">
+        <v>40</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="15.75" customHeight="1" s="18">
       <c r="A122" s="9" t="inlineStr">
@@ -6159,6 +7734,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>tomas.upton@example.com</t>
+        </is>
+      </c>
+      <c r="S122" t="n">
+        <v>18</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="15.75" customHeight="1" s="18">
       <c r="A123" s="9" t="inlineStr">
@@ -6205,6 +7793,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>ross.fairbanks@example.com</t>
+        </is>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="15.75" customHeight="1" s="18">
       <c r="A124" s="9" t="inlineStr">
@@ -6251,6 +7852,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>jonah.radcliffe@example.com</t>
+        </is>
+      </c>
+      <c r="S124" t="n">
+        <v>2</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="15.75" customHeight="1" s="18">
       <c r="A125" s="9" t="inlineStr">
@@ -6297,6 +7911,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>ivan.winterbourne@example.com</t>
+        </is>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="15.75" customHeight="1" s="18">
       <c r="A126" s="9" t="inlineStr">
@@ -6343,6 +7970,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>diego.northgate@example.com</t>
+        </is>
+      </c>
+      <c r="S126" t="n">
+        <v>16</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="15.75" customHeight="1" s="18">
       <c r="A127" s="9" t="inlineStr">
@@ -6389,6 +8029,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>karl.ashcombe@example.com</t>
+        </is>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="15.75" customHeight="1" s="18">
       <c r="A128" s="9" t="inlineStr">
@@ -6435,6 +8088,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>simon.pemberton@example.com</t>
+        </is>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="15.75" customHeight="1" s="18">
       <c r="A129" s="9" t="inlineStr">
@@ -6481,6 +8147,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>marcus.selwyn@example.com</t>
+        </is>
+      </c>
+      <c r="S129" t="n">
+        <v>37</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="15.75" customHeight="1" s="18">
       <c r="A130" s="9" t="inlineStr">
@@ -6527,6 +8206,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>martin.draper@example.com</t>
+        </is>
+      </c>
+      <c r="S130" t="n">
+        <v>6</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="15.75" customHeight="1" s="18">
       <c r="A131" s="9" t="inlineStr">
@@ -6573,6 +8265,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>raymond.jamison@example.com</t>
+        </is>
+      </c>
+      <c r="S131" t="n">
+        <v>29</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="15.75" customHeight="1" s="18">
       <c r="A132" s="9" t="inlineStr">
@@ -6619,6 +8324,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>vernon.hollingsworth@example.com</t>
+        </is>
+      </c>
+      <c r="S132" t="n">
+        <v>34</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="15.75" customHeight="1" s="18">
       <c r="A133" s="9" t="inlineStr">
@@ -6665,6 +8383,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>caleb.pemberton@example.com</t>
+        </is>
+      </c>
+      <c r="S133" t="n">
+        <v>9</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="15.75" customHeight="1" s="18">
       <c r="A134" s="9" t="inlineStr">
@@ -6711,6 +8442,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>cedric.zeigler@example.com</t>
+        </is>
+      </c>
+      <c r="S134" t="n">
+        <v>2</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="15.75" customHeight="1" s="18">
       <c r="A135" s="9" t="inlineStr">
@@ -6757,6 +8501,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>hugo.clayborne@example.com</t>
+        </is>
+      </c>
+      <c r="S135" t="n">
+        <v>23</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="15.75" customHeight="1" s="18">
       <c r="A136" s="9" t="inlineStr">
@@ -6803,6 +8560,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>ulysses.hollingsworth@example.com</t>
+        </is>
+      </c>
+      <c r="S136" t="n">
+        <v>20</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="15.75" customHeight="1" s="18">
       <c r="A137" s="9" t="inlineStr">
@@ -6849,6 +8619,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>wallace.pruitt@example.com</t>
+        </is>
+      </c>
+      <c r="S137" t="n">
+        <v>3</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="15.75" customHeight="1" s="18">
       <c r="A138" s="9" t="inlineStr">
@@ -6897,6 +8680,19 @@
       <c r="M138" s="0" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>andrei.upshaw@example.com</t>
+        </is>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6945,6 +8741,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>gavin.ellsworth@example.com</t>
+        </is>
+      </c>
+      <c r="S139" t="n">
+        <v>31</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="15.75" customHeight="1" s="18">
       <c r="A140" s="9" t="inlineStr">
@@ -6991,6 +8800,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>caleb.islington@example.com</t>
+        </is>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="15.75" customHeight="1" s="18">
       <c r="A141" s="9" t="inlineStr">
@@ -7037,6 +8859,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>erik.ostrander@example.com</t>
+        </is>
+      </c>
+      <c r="S141" t="n">
+        <v>9</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="15.75" customHeight="1" s="18">
       <c r="A142" s="9" t="inlineStr">
@@ -7083,6 +8918,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>luca.upton@example.com</t>
+        </is>
+      </c>
+      <c r="S142" t="n">
+        <v>5</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="15.75" customHeight="1" s="18">
       <c r="A143" s="9" t="inlineStr">
@@ -7129,6 +8977,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>ivan.hollowell@example.com</t>
+        </is>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="15.75" customHeight="1" s="18">
       <c r="A144" s="9" t="inlineStr">
@@ -7175,6 +9036,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>archer.nesbitt@example.com</t>
+        </is>
+      </c>
+      <c r="S144" t="n">
+        <v>3</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="15.75" customHeight="1" s="18">
       <c r="A145" s="9" t="inlineStr">
@@ -7221,6 +9095,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>henrik.harrington@example.com</t>
+        </is>
+      </c>
+      <c r="S145" t="n">
+        <v>9</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="15.75" customHeight="1" s="18">
       <c r="A146" s="9" t="inlineStr">
@@ -7267,6 +9154,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>quentin.stanton@example.com</t>
+        </is>
+      </c>
+      <c r="S146" t="n">
+        <v>22</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="15.75" customHeight="1" s="18">
       <c r="A147" s="9" t="inlineStr">
@@ -7313,6 +9213,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>grant.grimshaw@example.com</t>
+        </is>
+      </c>
+      <c r="S147" t="n">
+        <v>23</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="15.75" customHeight="1" s="18">
       <c r="A148" s="9" t="inlineStr">
@@ -7359,6 +9272,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>harold.zabriskie@example.com</t>
+        </is>
+      </c>
+      <c r="S148" t="n">
+        <v>6</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="15.75" customHeight="1" s="18">
       <c r="A149" s="9" t="inlineStr">
@@ -7405,6 +9331,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>wallace.lockhart@example.com</t>
+        </is>
+      </c>
+      <c r="S149" t="n">
+        <v>31</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="15.75" customHeight="1" s="18">
       <c r="A150" s="9" t="inlineStr">
@@ -7451,6 +9390,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>callum.tavish@example.com</t>
+        </is>
+      </c>
+      <c r="S150" t="n">
+        <v>27</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15.75" customHeight="1" s="18">
       <c r="A151" s="9" t="inlineStr">
@@ -7497,6 +9449,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>hamish.dunhill@example.com</t>
+        </is>
+      </c>
+      <c r="S151" t="n">
+        <v>2</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="15.75" customHeight="1" s="18">
       <c r="A152" s="9" t="inlineStr">
@@ -7545,6 +9510,19 @@
       <c r="M152" s="0" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>luigi.osborne@example.com</t>
+        </is>
+      </c>
+      <c r="S152" t="n">
+        <v>32</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -7593,6 +9571,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>nathan.lindqvist@example.com</t>
+        </is>
+      </c>
+      <c r="S153" t="n">
+        <v>37</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="15.75" customHeight="1" s="18">
       <c r="A154" s="8" t="inlineStr">
@@ -7636,6 +9627,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>mateo.fenwick@example.com</t>
+        </is>
+      </c>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="15.75" customHeight="1" s="18">
       <c r="A155" s="8" t="inlineStr">
@@ -7679,6 +9683,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>simon.yarrow@example.com</t>
+        </is>
+      </c>
+      <c r="S155" t="n">
+        <v>25</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="15.75" customHeight="1" s="18">
       <c r="A156" s="8" t="inlineStr">
@@ -7722,6 +9739,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>milan.upshaw@example.com</t>
+        </is>
+      </c>
+      <c r="S156" t="n">
+        <v>39</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="15.75" customHeight="1" s="18">
       <c r="A157" s="8" t="inlineStr">
@@ -7763,6 +9793,19 @@
       <c r="M157" s="0" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>terrence.prescott@example.com</t>
+        </is>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7784,6 +9827,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>nathaniel.pomeroy@example.com</t>
+        </is>
+      </c>
+      <c r="S158" t="n">
+        <v>6</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="15.75" customHeight="1" s="18">
       <c r="A159" s="0" t="inlineStr">
@@ -7840,6 +9896,14 @@
       <c r="N159" s="0" t="inlineStr">
         <is>
           <t>&lt;your profile link in the test community&gt;</t>
+        </is>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -20071,7 +22135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="130" customWidth="1" style="18" min="1" max="1"/>
@@ -20140,7 +22204,7 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>channel: 'none' = draft and review only, never sent. During setup, Fo fills in the tester row(s) with a real name and profile link and sets channel to 'skool'; only those rows can receive a real message.</t>
+          <t>channel: 'none' = draft and review only, never sent. During setup, Fo fills in the tester row(s) with a real name and email and sets channel to 'email'; only those rows can receive a real message.</t>
         </is>
       </c>
     </row>
@@ -20162,6 +22226,13 @@
       <c r="A13" s="0" t="inlineStr">
         <is>
           <t>Status history, Drafts, Conversions, Checks, Scorecard and Run log are written by Fo and Claude. Don't edit them by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>email, posts, intro_posted: from the member export. Emails here are fictional (example.com). posts = 0 and intro_posted = no means the member never got started.</t>
         </is>
       </c>
     </row>

--- a/demo/coaching-skool/demo-member-sheet.xlsx
+++ b/demo/coaching-skool/demo-member-sheet.xlsx
@@ -4,15 +4,16 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Touchpoints" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly pulse" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status history" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drafts" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conversions" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run log" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segments &amp; strategies" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Touchpoints" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly pulse" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status history" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drafts" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conversions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run log" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Members'!$A$1:$J$153</definedName>
@@ -442,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T994"/>
+  <dimension ref="A1:Z994"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="26" customWidth="1" style="18" min="1" max="1"/>
@@ -556,6 +557,36 @@
           <t>intro_posted</t>
         </is>
       </c>
+      <c r="U1" s="19" t="inlineStr">
+        <is>
+          <t>posts_30d</t>
+        </is>
+      </c>
+      <c r="V1" s="19" t="inlineStr">
+        <is>
+          <t>calls_attended_30d</t>
+        </is>
+      </c>
+      <c r="W1" s="19" t="inlineStr">
+        <is>
+          <t>goal_updated</t>
+        </is>
+      </c>
+      <c r="X1" s="19" t="inlineStr">
+        <is>
+          <t>recent_win</t>
+        </is>
+      </c>
+      <c r="Y1" s="19" t="inlineStr">
+        <is>
+          <t>recent_win_date</t>
+        </is>
+      </c>
+      <c r="Z1" s="19" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
@@ -606,17 +637,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="0" t="inlineStr">
         <is>
           <t>owen.fontaine@example.com</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="0" t="n">
         <v>29</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z2" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -649,7 +696,11 @@
         <f>IF(F3="","",TODAY()-F3)</f>
         <v/>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>pay off my credit card</t>
+        </is>
+      </c>
       <c r="I3" s="11" t="n"/>
       <c r="J3" s="11" t="n"/>
       <c r="K3" s="17" t="n">
@@ -665,15 +716,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" s="0" t="inlineStr">
         <is>
           <t>tomas.grimshaw@example.com</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="0" t="n">
         <v>36</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="0" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z3" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -724,17 +791,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R4" s="0" t="inlineStr">
         <is>
           <t>terrence.vanderbilt@example.com</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="S4" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T4" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U4" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z4" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -767,7 +845,11 @@
         <f>IF(F5="","",TODAY()-F5)</f>
         <v/>
       </c>
-      <c r="H5" s="11" t="n"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>pay off my credit card</t>
+        </is>
+      </c>
       <c r="I5" s="11" t="n"/>
       <c r="J5" s="11" t="n"/>
       <c r="K5" s="17" t="n">
@@ -783,17 +865,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R5" s="0" t="inlineStr">
         <is>
           <t>niklas.voss@example.com</t>
         </is>
       </c>
-      <c r="S5" t="n">
+      <c r="S5" s="0" t="n">
         <v>29</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T5" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U5" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="V5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z5" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -842,17 +940,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R6" s="0" t="inlineStr">
         <is>
           <t>quentin.wycliffe@example.com</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="S6" s="0" t="n">
         <v>33</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T6" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -901,17 +1010,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R7" s="0" t="inlineStr">
         <is>
           <t>vernon.bramwell@example.com</t>
         </is>
       </c>
-      <c r="S7" t="n">
-        <v>38</v>
-      </c>
-      <c r="T7" t="inlineStr">
+      <c r="S7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -960,15 +1080,26 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R8" s="0" t="inlineStr">
         <is>
           <t>basil.whitfield@example.com</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="S8" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T8" s="0" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1019,17 +1150,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R9" s="0" t="inlineStr">
         <is>
           <t>xavier.yates@example.com</t>
         </is>
       </c>
-      <c r="S9" t="n">
-        <v>12</v>
-      </c>
-      <c r="T9" t="inlineStr">
+      <c r="S9" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1086,17 +1228,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R10" s="0" t="inlineStr">
         <is>
           <t>franklin.hawthorne@example.com</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="S10" s="0" t="n">
         <v>33</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T10" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Z10" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1287,11 @@
         <f>IF(F11="","",TODAY()-F11)</f>
         <v/>
       </c>
-      <c r="H11" s="11" t="n"/>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>post on LinkedIn twice a week</t>
+        </is>
+      </c>
       <c r="I11" s="11" t="n"/>
       <c r="J11" s="11" t="n"/>
       <c r="K11" s="17" t="n">
@@ -1145,17 +1307,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R11" s="0" t="inlineStr">
         <is>
           <t>gavin.mumford@example.com</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="S11" s="0" t="n">
         <v>31</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T11" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z11" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1366,11 @@
         <f>IF(F12="","",TODAY()-F12)</f>
         <v/>
       </c>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>land 3 new consulting clients</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="11" t="n"/>
       <c r="K12" s="17" t="n">
@@ -1204,17 +1386,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R12" s="0" t="inlineStr">
         <is>
           <t>luigi.northgate@example.com</t>
         </is>
       </c>
-      <c r="S12" t="n">
-        <v>40</v>
-      </c>
-      <c r="T12" t="inlineStr">
+      <c r="S12" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="Z12" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1263,17 +1461,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R13" s="0" t="inlineStr">
         <is>
           <t>peter.sanderson@example.com</t>
         </is>
       </c>
-      <c r="S13" t="n">
+      <c r="S13" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T13" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1322,17 +1531,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R14" s="0" t="inlineStr">
         <is>
           <t>julius.yates@example.com</t>
         </is>
       </c>
-      <c r="S14" t="n">
-        <v>7</v>
-      </c>
-      <c r="T14" t="inlineStr">
+      <c r="S14" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1381,17 +1601,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R15" s="0" t="inlineStr">
         <is>
           <t>hamish.lindqvist@example.com</t>
         </is>
       </c>
-      <c r="S15" t="n">
+      <c r="S15" s="0" t="n">
         <v>29</v>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T15" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1655,11 @@
         <f>IF(F16="","",TODAY()-F16)</f>
         <v/>
       </c>
-      <c r="H16" s="11" t="n"/>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>finish my certification</t>
+        </is>
+      </c>
       <c r="I16" s="11" t="n"/>
       <c r="J16" s="11" t="n"/>
       <c r="K16" s="17" t="n">
@@ -1440,17 +1675,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R16" s="0" t="inlineStr">
         <is>
           <t>silas.quigley@example.com</t>
         </is>
       </c>
-      <c r="S16" t="n">
-        <v>20</v>
-      </c>
-      <c r="T16" t="inlineStr">
+      <c r="S16" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="Z16" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1734,11 @@
         <f>IF(F17="","",TODAY()-F17)</f>
         <v/>
       </c>
-      <c r="H17" s="11" t="n"/>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>get my first 1,000 followers</t>
+        </is>
+      </c>
       <c r="I17" s="11" t="n"/>
       <c r="J17" s="11" t="n"/>
       <c r="K17" s="17" t="n">
@@ -1499,17 +1754,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R17" s="0" t="inlineStr">
         <is>
           <t>padraig.fairbanks@example.com</t>
         </is>
       </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
+      <c r="S17" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="Z17" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1562,17 +1833,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R18" s="0" t="inlineStr">
         <is>
           <t>franklin.yarrow@example.com</t>
         </is>
       </c>
-      <c r="S18" t="n">
+      <c r="S18" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T18" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z18" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1621,17 +1908,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R19" s="0" t="inlineStr">
         <is>
           <t>stanley.pomeroy@example.com</t>
         </is>
       </c>
-      <c r="S19" t="n">
+      <c r="S19" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T19" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z19" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1680,17 +1978,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R20" s="0" t="inlineStr">
         <is>
           <t>caleb.ashford@example.com</t>
         </is>
       </c>
-      <c r="S20" t="n">
+      <c r="S20" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T20" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1739,17 +2048,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R21" s="0" t="inlineStr">
         <is>
           <t>derek.larimore@example.com</t>
         </is>
       </c>
-      <c r="S21" t="n">
+      <c r="S21" s="0" t="n">
         <v>39</v>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T21" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1798,17 +2118,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R22" s="0" t="inlineStr">
         <is>
           <t>enzo.ingram@example.com</t>
         </is>
       </c>
-      <c r="S22" t="n">
+      <c r="S22" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T22" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1857,17 +2188,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R23" s="0" t="inlineStr">
         <is>
           <t>andrei.upton@example.com</t>
         </is>
       </c>
-      <c r="S23" t="n">
+      <c r="S23" s="0" t="n">
         <v>29</v>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T23" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1916,17 +2258,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R24" s="0" t="inlineStr">
         <is>
           <t>anders.zeigler@example.com</t>
         </is>
       </c>
-      <c r="S24" t="n">
+      <c r="S24" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T24" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1979,17 +2332,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R25" s="0" t="inlineStr">
         <is>
           <t>duncan.jamison@example.com</t>
         </is>
       </c>
-      <c r="S25" t="n">
+      <c r="S25" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T25" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z25" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2391,11 @@
         <f>IF(F26="","",TODAY()-F26)</f>
         <v/>
       </c>
-      <c r="H26" s="11" t="n"/>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>get my side project to 100 users</t>
+        </is>
+      </c>
       <c r="I26" s="11" t="n"/>
       <c r="J26" s="11" t="n"/>
       <c r="K26" s="17" t="n">
@@ -2038,17 +2411,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R26" s="0" t="inlineStr">
         <is>
           <t>karl.rowntree@example.com</t>
         </is>
       </c>
-      <c r="S26" t="n">
-        <v>40</v>
-      </c>
-      <c r="T26" t="inlineStr">
+      <c r="S26" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="Z26" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2470,11 @@
         <f>IF(F27="","",TODAY()-F27)</f>
         <v/>
       </c>
-      <c r="H27" s="11" t="n"/>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>get my side project to 100 users</t>
+        </is>
+      </c>
       <c r="I27" s="11" t="n"/>
       <c r="J27" s="11" t="n"/>
       <c r="K27" s="17" t="n">
@@ -2097,17 +2490,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R27" s="0" t="inlineStr">
         <is>
           <t>micah.yardley@example.com</t>
         </is>
       </c>
-      <c r="S27" t="n">
+      <c r="S27" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T27" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="W27" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z27" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2156,17 +2565,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R28" s="0" t="inlineStr">
         <is>
           <t>rafael.huxley@example.com</t>
         </is>
       </c>
-      <c r="S28" t="n">
+      <c r="S28" s="0" t="n">
         <v>34</v>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T28" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z28" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2215,17 +2635,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R29" s="0" t="inlineStr">
         <is>
           <t>xavier.jernigan@example.com</t>
         </is>
       </c>
-      <c r="S29" t="n">
+      <c r="S29" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T29" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U29" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V29" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z29" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2274,17 +2705,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R30" s="0" t="inlineStr">
         <is>
           <t>luigi.winslow@example.com</t>
         </is>
       </c>
-      <c r="S30" t="n">
+      <c r="S30" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T30" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U30" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V30" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z30" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2333,17 +2775,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R31" s="0" t="inlineStr">
         <is>
           <t>rowan.ridgeway@example.com</t>
         </is>
       </c>
-      <c r="S31" t="n">
+      <c r="S31" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T31" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2392,17 +2845,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="R32" s="0" t="inlineStr">
         <is>
           <t>silas.ingram@example.com</t>
         </is>
       </c>
-      <c r="S32" t="n">
+      <c r="S32" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T32" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z32" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2451,15 +2915,26 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="R33" s="0" t="inlineStr">
         <is>
           <t>lars.glendower@example.com</t>
         </is>
       </c>
-      <c r="S33" t="n">
+      <c r="S33" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="T33" s="0" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -2494,7 +2969,11 @@
         <f>IF(F34="","",TODAY()-F34)</f>
         <v/>
       </c>
-      <c r="H34" s="11" t="n"/>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>build a morning routine and keep it for 90 days</t>
+        </is>
+      </c>
       <c r="I34" s="11" t="n"/>
       <c r="J34" s="11" t="inlineStr">
         <is>
@@ -2514,17 +2993,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="R34" s="0" t="inlineStr">
         <is>
           <t>terrence.lachlan@example.com</t>
         </is>
       </c>
-      <c r="S34" t="n">
+      <c r="S34" s="0" t="n">
         <v>39</v>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="T34" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="W34" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z34" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2573,17 +3068,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="R35" s="0" t="inlineStr">
         <is>
           <t>ivan.montgomery@example.com</t>
         </is>
       </c>
-      <c r="S35" t="n">
+      <c r="S35" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T35" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U35" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="V35" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z35" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2616,7 +3122,11 @@
         <f>IF(F36="","",TODAY()-F36)</f>
         <v/>
       </c>
-      <c r="H36" s="11" t="n"/>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>launch a paid workshop</t>
+        </is>
+      </c>
       <c r="I36" s="11" t="n"/>
       <c r="J36" s="11" t="n"/>
       <c r="K36" s="17" t="n">
@@ -2632,17 +3142,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="R36" s="0" t="inlineStr">
         <is>
           <t>xavier.ashford@example.com</t>
         </is>
       </c>
-      <c r="S36" t="n">
+      <c r="S36" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T36" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z36" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2691,17 +3217,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="R37" s="0" t="inlineStr">
         <is>
           <t>mateo.calloway@example.com</t>
         </is>
       </c>
-      <c r="S37" t="n">
+      <c r="S37" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T37" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2750,17 +3287,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="R38" s="0" t="inlineStr">
         <is>
           <t>peter.jamison@example.com</t>
         </is>
       </c>
-      <c r="S38" t="n">
+      <c r="S38" s="0" t="n">
         <v>29</v>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T38" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U38" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V38" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z38" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2809,17 +3357,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R39" s="0" t="inlineStr">
         <is>
           <t>levi.pruitt@example.com</t>
         </is>
       </c>
-      <c r="S39" t="n">
+      <c r="S39" s="0" t="n">
         <v>38</v>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="T39" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2872,17 +3431,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="R40" s="0" t="inlineStr">
         <is>
           <t>padraig.fairview@example.com</t>
         </is>
       </c>
-      <c r="S40" t="n">
+      <c r="S40" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="T40" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z40" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2915,7 +3490,11 @@
         <f>IF(F41="","",TODAY()-F41)</f>
         <v/>
       </c>
-      <c r="H41" s="11" t="n"/>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>launch my coaching offer by December</t>
+        </is>
+      </c>
       <c r="I41" s="11" t="n"/>
       <c r="J41" s="11" t="n"/>
       <c r="K41" s="17" t="n">
@@ -2931,17 +3510,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="R41" s="0" t="inlineStr">
         <is>
           <t>angus.quigley@example.com</t>
         </is>
       </c>
-      <c r="S41" t="n">
+      <c r="S41" s="0" t="n">
         <v>34</v>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="T41" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="W41" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z41" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2990,17 +3585,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R42" s="0" t="inlineStr">
         <is>
           <t>harold.tavish@example.com</t>
         </is>
       </c>
-      <c r="S42" t="n">
+      <c r="S42" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T42" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3639,11 @@
         <f>IF(F43="","",TODAY()-F43)</f>
         <v/>
       </c>
-      <c r="H43" s="11" t="n"/>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>get comfortable speaking on stage</t>
+        </is>
+      </c>
       <c r="I43" s="11" t="n"/>
       <c r="J43" s="11" t="n"/>
       <c r="K43" s="17" t="n">
@@ -3049,17 +3659,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R43" s="0" t="inlineStr">
         <is>
           <t>edmund.grimshaw@example.com</t>
         </is>
       </c>
-      <c r="S43" t="n">
+      <c r="S43" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T43" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z43" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3108,17 +3734,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="R44" s="0" t="inlineStr">
         <is>
           <t>callum.dunhill@example.com</t>
         </is>
       </c>
-      <c r="S44" t="n">
+      <c r="S44" s="0" t="n">
         <v>32</v>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T44" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U44" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="V44" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z44" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3788,11 @@
         <f>IF(F45="","",TODAY()-F45)</f>
         <v/>
       </c>
-      <c r="H45" s="11" t="n"/>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>finish the first draft of my book</t>
+        </is>
+      </c>
       <c r="I45" s="11" t="n"/>
       <c r="J45" s="11" t="n"/>
       <c r="K45" s="17" t="n">
@@ -3167,17 +3808,43 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="R45" s="0" t="inlineStr">
         <is>
           <t>levi.yardley@example.com</t>
         </is>
       </c>
-      <c r="S45" t="n">
+      <c r="S45" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T45" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U45" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="X45" s="0" t="inlineStr">
+        <is>
+          <t>got promoted</t>
+        </is>
+      </c>
+      <c r="Y45" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z45" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3877,11 @@
         <f>IF(F46="","",TODAY()-F46)</f>
         <v/>
       </c>
-      <c r="H46" s="11" t="n"/>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>record 10 podcast episodes</t>
+        </is>
+      </c>
       <c r="I46" s="11" t="n"/>
       <c r="J46" s="11" t="n"/>
       <c r="K46" s="17" t="n">
@@ -3226,17 +3897,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="R46" s="0" t="inlineStr">
         <is>
           <t>xavier.ingram@example.com</t>
         </is>
       </c>
-      <c r="S46" t="n">
+      <c r="S46" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T46" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z46" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3956,11 @@
         <f>IF(F47="","",TODAY()-F47)</f>
         <v/>
       </c>
-      <c r="H47" s="11" t="n"/>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>start a weekly newsletter</t>
+        </is>
+      </c>
       <c r="I47" s="11" t="n"/>
       <c r="J47" s="11" t="n"/>
       <c r="K47" s="17" t="n">
@@ -3285,17 +3976,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="R47" s="0" t="inlineStr">
         <is>
           <t>nathaniel.quimby@example.com</t>
         </is>
       </c>
-      <c r="S47" t="n">
+      <c r="S47" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="T47" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U47" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V47" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="W47" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z47" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3344,17 +4051,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="R48" s="0" t="inlineStr">
         <is>
           <t>derek.sinclair@example.com</t>
         </is>
       </c>
-      <c r="S48" t="n">
+      <c r="S48" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="T48" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3403,17 +4121,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="R49" s="0" t="inlineStr">
         <is>
           <t>andre.marlowe@example.com</t>
         </is>
       </c>
-      <c r="S49" t="n">
+      <c r="S49" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="T49" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z49" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3446,7 +4175,11 @@
         <f>IF(F50="","",TODAY()-F50)</f>
         <v/>
       </c>
-      <c r="H50" s="11" t="n"/>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>get my first 1,000 followers</t>
+        </is>
+      </c>
       <c r="I50" s="11" t="n"/>
       <c r="J50" s="11" t="n"/>
       <c r="K50" s="17" t="n">
@@ -3462,17 +4195,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="R50" s="0" t="inlineStr">
         <is>
           <t>clifford.quimby@example.com</t>
         </is>
       </c>
-      <c r="S50" t="n">
+      <c r="S50" s="0" t="n">
         <v>36</v>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="T50" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z50" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3521,17 +4270,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="R51" s="0" t="inlineStr">
         <is>
           <t>clifford.eastwood@example.com</t>
         </is>
       </c>
-      <c r="S51" t="n">
+      <c r="S51" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="T51" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U51" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="V51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3580,17 +4340,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="R52" s="0" t="inlineStr">
         <is>
           <t>angus.orchard@example.com</t>
         </is>
       </c>
-      <c r="S52" t="n">
+      <c r="S52" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="T52" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3623,7 +4394,11 @@
         <f>IF(F53="","",TODAY()-F53)</f>
         <v/>
       </c>
-      <c r="H53" s="11" t="n"/>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>record 10 podcast episodes</t>
+        </is>
+      </c>
       <c r="I53" s="11" t="n"/>
       <c r="J53" s="11" t="n"/>
       <c r="K53" s="17" t="n">
@@ -3639,17 +4414,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="R53" s="0" t="inlineStr">
         <is>
           <t>stefan.fairview@example.com</t>
         </is>
       </c>
-      <c r="S53" t="n">
+      <c r="S53" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="T53" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z53" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3702,17 +4493,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="R54" s="0" t="inlineStr">
         <is>
           <t>malcolm.corbin@example.com</t>
         </is>
       </c>
-      <c r="S54" t="n">
+      <c r="S54" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="T54" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z54" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3761,17 +4568,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="R55" s="0" t="inlineStr">
         <is>
           <t>oscar.fenwick@example.com</t>
         </is>
       </c>
-      <c r="S55" t="n">
+      <c r="S55" s="0" t="n">
         <v>33</v>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="T55" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U55" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="V55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3820,17 +4638,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="R56" s="0" t="inlineStr">
         <is>
           <t>adam.carmichael@example.com</t>
         </is>
       </c>
-      <c r="S56" t="n">
+      <c r="S56" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="T56" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U56" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="V56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3879,17 +4708,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="R57" s="0" t="inlineStr">
         <is>
           <t>andrei.pruitt@example.com</t>
         </is>
       </c>
-      <c r="S57" t="n">
+      <c r="S57" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="T57" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3938,15 +4778,26 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="R58" s="0" t="inlineStr">
         <is>
           <t>cedric.montgomery@example.com</t>
         </is>
       </c>
-      <c r="S58" t="n">
+      <c r="S58" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="T58" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3997,17 +4848,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="R59" s="0" t="inlineStr">
         <is>
           <t>jonah.thornbury@example.com</t>
         </is>
       </c>
-      <c r="S59" t="n">
+      <c r="S59" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="T59" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4902,11 @@
         <f>IF(F60="","",TODAY()-F60)</f>
         <v/>
       </c>
-      <c r="H60" s="11" t="n"/>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>post on LinkedIn twice a week</t>
+        </is>
+      </c>
       <c r="I60" s="11" t="n"/>
       <c r="J60" s="11" t="inlineStr">
         <is>
@@ -4060,15 +4926,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="R60" s="0" t="inlineStr">
         <is>
           <t>owen.yandell@example.com</t>
         </is>
       </c>
-      <c r="S60" t="n">
+      <c r="S60" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="T60" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="W60" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z60" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4119,17 +5001,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="R61" s="0" t="inlineStr">
         <is>
           <t>colin.zabriskie@example.com</t>
         </is>
       </c>
-      <c r="S61" t="n">
+      <c r="S61" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="T61" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U61" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="V61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z61" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -4162,7 +5055,11 @@
         <f>IF(F62="","",TODAY()-F62)</f>
         <v/>
       </c>
-      <c r="H62" s="11" t="n"/>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>launch my coaching offer by December</t>
+        </is>
+      </c>
       <c r="I62" s="11" t="n"/>
       <c r="J62" s="11" t="n"/>
       <c r="K62" s="17" t="n">
@@ -4178,17 +5075,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="R62" s="0" t="inlineStr">
         <is>
           <t>raymond.elbridge@example.com</t>
         </is>
       </c>
-      <c r="S62" t="n">
+      <c r="S62" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="T62" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U62" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="V62" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="W62" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z62" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -4237,15 +5150,26 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="R63" s="0" t="inlineStr">
         <is>
           <t>julian.northgate@example.com</t>
         </is>
       </c>
-      <c r="S63" t="n">
+      <c r="S63" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="T63" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4280,7 +5204,11 @@
         <f>IF(F64="","",TODAY()-F64)</f>
         <v/>
       </c>
-      <c r="H64" s="11" t="n"/>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>get comfortable speaking on stage</t>
+        </is>
+      </c>
       <c r="I64" s="11" t="n"/>
       <c r="J64" s="11" t="n"/>
       <c r="K64" s="17" t="n">
@@ -4296,17 +5224,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="R64" s="0" t="inlineStr">
         <is>
           <t>colin.thornbury@example.com</t>
         </is>
       </c>
-      <c r="S64" t="n">
+      <c r="S64" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="T64" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U64" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="V64" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="W64" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z64" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -4355,17 +5299,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="R65" s="0" t="inlineStr">
         <is>
           <t>inigo.corbin@example.com</t>
         </is>
       </c>
-      <c r="S65" t="n">
+      <c r="S65" s="0" t="n">
         <v>31</v>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="T65" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U65" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="V65" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -4418,17 +5373,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="R66" s="0" t="inlineStr">
         <is>
           <t>colin.winterbourne@example.com</t>
         </is>
       </c>
-      <c r="S66" t="n">
+      <c r="S66" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="T66" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" s="0" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z66" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -4461,7 +5432,11 @@
         <f>IF(F67="","",TODAY()-F67)</f>
         <v/>
       </c>
-      <c r="H67" s="11" t="n"/>
+      <c r="H67" s="11" t="inlineStr">
+        <is>
+          <t>finish my certification</t>
+        </is>
+      </c>
       <c r="I67" s="11" t="n"/>
       <c r="J67" s="11" t="n"/>
       <c r="K67" s="17" t="n">
@@ -4477,17 +5452,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="R67" s="0" t="inlineStr">
         <is>
           <t>kendrick.kessler@example.com</t>
         </is>
       </c>
-      <c r="S67" t="n">
+      <c r="S67" s="0" t="n">
         <v>37</v>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="T67" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U67" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="V67" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="W67" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z67" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -4520,7 +5511,11 @@
         <f>IF(F68="","",TODAY()-F68)</f>
         <v/>
       </c>
-      <c r="H68" s="11" t="n"/>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>hire a part-time assistant</t>
+        </is>
+      </c>
       <c r="I68" s="11" t="n"/>
       <c r="J68" s="11" t="n"/>
       <c r="K68" s="17" t="n">
@@ -4536,17 +5531,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="R68" s="0" t="inlineStr">
         <is>
           <t>peter.thornbury@example.com</t>
         </is>
       </c>
-      <c r="S68" t="n">
+      <c r="S68" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="T68" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U68" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="V68" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z68" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -4595,17 +5606,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="R69" s="0" t="inlineStr">
         <is>
           <t>emmett.wycliffe@example.com</t>
         </is>
       </c>
-      <c r="S69" t="n">
+      <c r="S69" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="T69" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U69" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -4654,17 +5676,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="R70" s="0" t="inlineStr">
         <is>
           <t>hugo.ridgeway@example.com</t>
         </is>
       </c>
-      <c r="S70" t="n">
+      <c r="S70" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="T70" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U70" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -4713,17 +5746,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="R71" s="0" t="inlineStr">
         <is>
           <t>levi.quimby@example.com</t>
         </is>
       </c>
-      <c r="S71" t="n">
+      <c r="S71" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="T71" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U71" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="V71" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z71" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -4756,7 +5800,11 @@
         <f>IF(F72="","",TODAY()-F72)</f>
         <v/>
       </c>
-      <c r="H72" s="11" t="n"/>
+      <c r="H72" s="11" t="inlineStr">
+        <is>
+          <t>get comfortable speaking on stage</t>
+        </is>
+      </c>
       <c r="I72" s="11" t="n"/>
       <c r="J72" s="11" t="n"/>
       <c r="K72" s="17" t="n">
@@ -4772,15 +5820,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="R72" s="0" t="inlineStr">
         <is>
           <t>hamish.oakeshott@example.com</t>
         </is>
       </c>
-      <c r="S72" t="n">
+      <c r="S72" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="T72" s="0" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U72" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Z72" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -4815,7 +5879,11 @@
         <f>IF(F73="","",TODAY()-F73)</f>
         <v/>
       </c>
-      <c r="H73" s="11" t="n"/>
+      <c r="H73" s="11" t="inlineStr">
+        <is>
+          <t>launch my coaching offer by December</t>
+        </is>
+      </c>
       <c r="I73" s="11" t="n"/>
       <c r="J73" s="11" t="n"/>
       <c r="K73" s="17" t="n">
@@ -4831,15 +5899,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="R73" s="0" t="inlineStr">
         <is>
           <t>quentin.lindqvist@example.com</t>
         </is>
       </c>
-      <c r="S73" t="n">
+      <c r="S73" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="T73" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U73" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Z73" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4894,17 +5978,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="R74" s="0" t="inlineStr">
         <is>
           <t>wallace.pemberton@example.com</t>
         </is>
       </c>
-      <c r="S74" t="n">
+      <c r="S74" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="T74" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U74" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z74" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -4953,15 +6053,26 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="R75" s="0" t="inlineStr">
         <is>
           <t>xavier.garrick@example.com</t>
         </is>
       </c>
-      <c r="S75" t="n">
+      <c r="S75" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="T75" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U75" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z75" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5012,17 +6123,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="R76" s="0" t="inlineStr">
         <is>
           <t>marco.mowbray@example.com</t>
         </is>
       </c>
-      <c r="S76" t="n">
+      <c r="S76" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="T76" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U76" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V76" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z76" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5071,17 +6193,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="R77" s="0" t="inlineStr">
         <is>
           <t>terrence.islington@example.com</t>
         </is>
       </c>
-      <c r="S77" t="n">
+      <c r="S77" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="T77" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U77" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="V77" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z77" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5130,17 +6263,38 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="R78" s="0" t="inlineStr">
         <is>
           <t>peter.fairview@example.com</t>
         </is>
       </c>
-      <c r="S78" t="n">
+      <c r="S78" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="T78" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U78" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V78" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" s="0" t="inlineStr">
+        <is>
+          <t>raised prices and nobody left</t>
+        </is>
+      </c>
+      <c r="Y78" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z78" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5193,17 +6347,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="R79" s="0" t="inlineStr">
         <is>
           <t>enzo.pomeroy@example.com</t>
         </is>
       </c>
-      <c r="S79" t="n">
+      <c r="S79" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="T79" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U79" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z79" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5252,17 +6422,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="R80" s="0" t="inlineStr">
         <is>
           <t>callum.norwood@example.com</t>
         </is>
       </c>
-      <c r="S80" t="n">
+      <c r="S80" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="T80" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U80" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V80" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z80" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5311,15 +6492,26 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="R81" s="0" t="inlineStr">
         <is>
           <t>tomas.kirkland@example.com</t>
         </is>
       </c>
-      <c r="S81" t="n">
+      <c r="S81" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="T81" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U81" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z81" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5354,7 +6546,11 @@
         <f>IF(F82="","",TODAY()-F82)</f>
         <v/>
       </c>
-      <c r="H82" s="11" t="n"/>
+      <c r="H82" s="11" t="inlineStr">
+        <is>
+          <t>land 3 new consulting clients</t>
+        </is>
+      </c>
       <c r="I82" s="11" t="n"/>
       <c r="J82" s="11" t="n"/>
       <c r="K82" s="17" t="n">
@@ -5370,17 +6566,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="R82" s="0" t="inlineStr">
         <is>
           <t>terrence.quimby@example.com</t>
         </is>
       </c>
-      <c r="S82" t="n">
+      <c r="S82" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="T82" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U82" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="W82" s="0" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z82" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5413,7 +6625,11 @@
         <f>IF(F83="","",TODAY()-F83)</f>
         <v/>
       </c>
-      <c r="H83" s="11" t="n"/>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>pay off my credit card</t>
+        </is>
+      </c>
       <c r="I83" s="11" t="n"/>
       <c r="J83" s="11" t="n"/>
       <c r="K83" s="17" t="n">
@@ -5429,15 +6645,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="R83" s="0" t="inlineStr">
         <is>
           <t>fraser.islington@example.com</t>
         </is>
       </c>
-      <c r="S83" t="n">
+      <c r="S83" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="T83" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U83" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="W83" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z83" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5488,17 +6720,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="R84" s="0" t="inlineStr">
         <is>
           <t>julian.quimby@example.com</t>
         </is>
       </c>
-      <c r="S84" t="n">
+      <c r="S84" s="0" t="n">
         <v>38</v>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="T84" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U84" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V84" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5551,17 +6794,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="R85" s="0" t="inlineStr">
         <is>
           <t>mateo.fairbanks@example.com</t>
         </is>
       </c>
-      <c r="S85" t="n">
+      <c r="S85" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="T85" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U85" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z85" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5594,7 +6853,11 @@
         <f>IF(F86="","",TODAY()-F86)</f>
         <v/>
       </c>
-      <c r="H86" s="11" t="n"/>
+      <c r="H86" s="11" t="inlineStr">
+        <is>
+          <t>hire a part-time assistant</t>
+        </is>
+      </c>
       <c r="I86" s="11" t="n"/>
       <c r="J86" s="11" t="n"/>
       <c r="K86" s="17" t="n">
@@ -5610,15 +6873,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="R86" s="0" t="inlineStr">
         <is>
           <t>fraser.sanderson@example.com</t>
         </is>
       </c>
-      <c r="S86" t="n">
+      <c r="S86" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="T86" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U86" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="W86" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z86" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5669,17 +6948,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="R87" s="0" t="inlineStr">
         <is>
           <t>fraser.ironside@example.com</t>
         </is>
       </c>
-      <c r="S87" t="n">
+      <c r="S87" s="0" t="n">
         <v>39</v>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="T87" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U87" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z87" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5712,7 +7002,11 @@
         <f>IF(F88="","",TODAY()-F88)</f>
         <v/>
       </c>
-      <c r="H88" s="11" t="n"/>
+      <c r="H88" s="11" t="inlineStr">
+        <is>
+          <t>record 10 podcast episodes</t>
+        </is>
+      </c>
       <c r="I88" s="11" t="n"/>
       <c r="J88" s="11" t="n"/>
       <c r="K88" s="17" t="n">
@@ -5728,17 +7022,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="R88" s="0" t="inlineStr">
         <is>
           <t>wallace.clayborne@example.com</t>
         </is>
       </c>
-      <c r="S88" t="n">
+      <c r="S88" s="0" t="n">
         <v>37</v>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="T88" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U88" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V88" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z88" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5771,7 +7081,11 @@
         <f>IF(F89="","",TODAY()-F89)</f>
         <v/>
       </c>
-      <c r="H89" s="11" t="n"/>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>finish the first draft of my book</t>
+        </is>
+      </c>
       <c r="I89" s="11" t="n"/>
       <c r="J89" s="11" t="n"/>
       <c r="K89" s="17" t="n">
@@ -5787,17 +7101,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="R89" s="0" t="inlineStr">
         <is>
           <t>andre.zeigler@example.com</t>
         </is>
       </c>
-      <c r="S89" t="n">
+      <c r="S89" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="T89" t="inlineStr">
+      <c r="T89" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U89" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="W89" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z89" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5846,15 +7176,26 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="R90" s="0" t="inlineStr">
         <is>
           <t>duncan.ironside@example.com</t>
         </is>
       </c>
-      <c r="S90" t="n">
+      <c r="S90" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T90" t="inlineStr">
+      <c r="T90" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U90" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5889,7 +7230,11 @@
         <f>IF(F91="","",TODAY()-F91)</f>
         <v/>
       </c>
-      <c r="H91" s="11" t="n"/>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>move from freelance to a full-time role</t>
+        </is>
+      </c>
       <c r="I91" s="11" t="n"/>
       <c r="J91" s="11" t="n"/>
       <c r="K91" s="17" t="n">
@@ -5905,15 +7250,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="R91" s="0" t="inlineStr">
         <is>
           <t>julian.waverly@example.com</t>
         </is>
       </c>
-      <c r="S91" t="n">
+      <c r="S91" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T91" t="inlineStr">
+      <c r="T91" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U91" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="W91" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z91" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5948,7 +7309,11 @@
         <f>IF(F92="","",TODAY()-F92)</f>
         <v/>
       </c>
-      <c r="H92" s="11" t="n"/>
+      <c r="H92" s="11" t="inlineStr">
+        <is>
+          <t>launch a paid workshop</t>
+        </is>
+      </c>
       <c r="I92" s="11" t="n"/>
       <c r="J92" s="11" t="n"/>
       <c r="K92" s="17" t="n">
@@ -5964,17 +7329,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="R92" s="0" t="inlineStr">
         <is>
           <t>silas.hawthorne@example.com</t>
         </is>
       </c>
-      <c r="S92" t="n">
+      <c r="S92" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="T92" t="inlineStr">
+      <c r="T92" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U92" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z92" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6007,7 +7388,11 @@
         <f>IF(F93="","",TODAY()-F93)</f>
         <v/>
       </c>
-      <c r="H93" s="11" t="n"/>
+      <c r="H93" s="11" t="inlineStr">
+        <is>
+          <t>build a morning routine and keep it for 90 days</t>
+        </is>
+      </c>
       <c r="I93" s="11" t="n"/>
       <c r="J93" s="11" t="n"/>
       <c r="K93" s="17" t="n">
@@ -6023,17 +7408,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
+      <c r="R93" s="0" t="inlineStr">
         <is>
           <t>nathan.pemberton@example.com</t>
         </is>
       </c>
-      <c r="S93" t="n">
+      <c r="S93" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="T93" t="inlineStr">
+      <c r="T93" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U93" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z93" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6066,7 +7467,11 @@
         <f>IF(F94="","",TODAY()-F94)</f>
         <v/>
       </c>
-      <c r="H94" s="11" t="n"/>
+      <c r="H94" s="11" t="inlineStr">
+        <is>
+          <t>move from freelance to a full-time role</t>
+        </is>
+      </c>
       <c r="I94" s="11" t="n"/>
       <c r="J94" s="11" t="n"/>
       <c r="K94" s="17" t="n">
@@ -6082,17 +7487,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="R94" s="0" t="inlineStr">
         <is>
           <t>paolo.sanderson@example.com</t>
         </is>
       </c>
-      <c r="S94" t="n">
+      <c r="S94" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="T94" t="inlineStr">
+      <c r="T94" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U94" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="V94" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="W94" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z94" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6141,17 +7562,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="R95" s="0" t="inlineStr">
         <is>
           <t>emmett.sinclair@example.com</t>
         </is>
       </c>
-      <c r="S95" t="n">
+      <c r="S95" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="T95" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U95" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6184,7 +7616,11 @@
         <f>IF(F96="","",TODAY()-F96)</f>
         <v/>
       </c>
-      <c r="H96" s="11" t="n"/>
+      <c r="H96" s="11" t="inlineStr">
+        <is>
+          <t>write every morning for 30 days</t>
+        </is>
+      </c>
       <c r="I96" s="11" t="n"/>
       <c r="J96" s="11" t="n"/>
       <c r="K96" s="17" t="n">
@@ -6200,15 +7636,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr">
+      <c r="R96" s="0" t="inlineStr">
         <is>
           <t>clifford.cranfield@example.com</t>
         </is>
       </c>
-      <c r="S96" t="n">
+      <c r="S96" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T96" t="inlineStr">
+      <c r="T96" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U96" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="W96" s="0" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z96" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -6259,17 +7711,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="R97" s="0" t="inlineStr">
         <is>
           <t>marcus.radcliffe@example.com</t>
         </is>
       </c>
-      <c r="S97" t="n">
+      <c r="S97" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="T97" t="inlineStr">
+      <c r="T97" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U97" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6318,15 +7781,26 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr">
+      <c r="R98" s="0" t="inlineStr">
         <is>
           <t>franklin.thornbury@example.com</t>
         </is>
       </c>
-      <c r="S98" t="n">
+      <c r="S98" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T98" t="inlineStr">
+      <c r="T98" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U98" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -6361,7 +7835,11 @@
         <f>IF(F99="","",TODAY()-F99)</f>
         <v/>
       </c>
-      <c r="H99" s="11" t="n"/>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>raise my prices with existing clients</t>
+        </is>
+      </c>
       <c r="I99" s="11" t="n"/>
       <c r="J99" s="11" t="n"/>
       <c r="K99" s="17" t="n">
@@ -6377,17 +7855,43 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="R99" s="0" t="inlineStr">
         <is>
           <t>leonard.whitfield@example.com</t>
         </is>
       </c>
-      <c r="S99" t="n">
+      <c r="S99" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="T99" t="inlineStr">
+      <c r="T99" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U99" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V99" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" s="0" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="X99" s="0" t="inlineStr">
+        <is>
+          <t>launched the beta</t>
+        </is>
+      </c>
+      <c r="Y99" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z99" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6436,17 +7940,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr">
+      <c r="R100" s="0" t="inlineStr">
         <is>
           <t>rowan.jetley@example.com</t>
         </is>
       </c>
-      <c r="S100" t="n">
+      <c r="S100" s="0" t="n">
         <v>38</v>
       </c>
-      <c r="T100" t="inlineStr">
+      <c r="T100" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U100" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6479,7 +7994,11 @@
         <f>IF(F101="","",TODAY()-F101)</f>
         <v/>
       </c>
-      <c r="H101" s="11" t="n"/>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>launch a paid workshop</t>
+        </is>
+      </c>
       <c r="I101" s="11" t="n"/>
       <c r="J101" s="11" t="n"/>
       <c r="K101" s="17" t="n">
@@ -6495,17 +8014,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr">
+      <c r="R101" s="0" t="inlineStr">
         <is>
           <t>julius.jardine@example.com</t>
         </is>
       </c>
-      <c r="S101" t="n">
+      <c r="S101" s="0" t="n">
         <v>37</v>
       </c>
-      <c r="T101" t="inlineStr">
+      <c r="T101" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U101" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="W101" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z101" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6538,7 +8073,11 @@
         <f>IF(F102="","",TODAY()-F102)</f>
         <v/>
       </c>
-      <c r="H102" s="11" t="n"/>
+      <c r="H102" s="11" t="inlineStr">
+        <is>
+          <t>get my side project to 100 users</t>
+        </is>
+      </c>
       <c r="I102" s="11" t="n"/>
       <c r="J102" s="11" t="n"/>
       <c r="K102" s="17" t="n">
@@ -6554,15 +8093,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr">
+      <c r="R102" s="0" t="inlineStr">
         <is>
           <t>lars.underhill@example.com</t>
         </is>
       </c>
-      <c r="S102" t="n">
+      <c r="S102" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T102" t="inlineStr">
+      <c r="T102" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U102" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="W102" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Z102" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -6613,17 +8168,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr">
+      <c r="R103" s="0" t="inlineStr">
         <is>
           <t>nathaniel.lachlan@example.com</t>
         </is>
       </c>
-      <c r="S103" t="n">
+      <c r="S103" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="T103" t="inlineStr">
+      <c r="T103" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U103" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V103" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z103" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6656,7 +8222,11 @@
         <f>IF(F104="","",TODAY()-F104)</f>
         <v/>
       </c>
-      <c r="H104" s="11" t="n"/>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>write every morning for 30 days</t>
+        </is>
+      </c>
       <c r="I104" s="11" t="n"/>
       <c r="J104" s="11" t="n"/>
       <c r="K104" s="17" t="n">
@@ -6672,17 +8242,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="R104" s="0" t="inlineStr">
         <is>
           <t>grant.ridgeway@example.com</t>
         </is>
       </c>
-      <c r="S104" t="n">
+      <c r="S104" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="T104" t="inlineStr">
+      <c r="T104" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U104" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="V104" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="W104" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z104" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6731,17 +8317,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="R105" s="0" t="inlineStr">
         <is>
           <t>tomas.hollingsworth@example.com</t>
         </is>
       </c>
-      <c r="S105" t="n">
+      <c r="S105" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="T105" t="inlineStr">
+      <c r="T105" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U105" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6790,17 +8387,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr">
+      <c r="R106" s="0" t="inlineStr">
         <is>
           <t>silas.fairview@example.com</t>
         </is>
       </c>
-      <c r="S106" t="n">
+      <c r="S106" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="T106" t="inlineStr">
+      <c r="T106" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U106" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6833,7 +8441,11 @@
         <f>IF(F107="","",TODAY()-F107)</f>
         <v/>
       </c>
-      <c r="H107" s="11" t="n"/>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>pay off my credit card</t>
+        </is>
+      </c>
       <c r="I107" s="11" t="n"/>
       <c r="J107" s="11" t="n"/>
       <c r="K107" s="17" t="n">
@@ -6849,15 +8461,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr">
+      <c r="R107" s="0" t="inlineStr">
         <is>
           <t>franklin.orchard@example.com</t>
         </is>
       </c>
-      <c r="S107" t="n">
+      <c r="S107" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T107" t="inlineStr">
+      <c r="T107" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U107" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="W107" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z107" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -6908,17 +8536,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr">
+      <c r="R108" s="0" t="inlineStr">
         <is>
           <t>martin.lindqvist@example.com</t>
         </is>
       </c>
-      <c r="S108" t="n">
+      <c r="S108" s="0" t="n">
         <v>36</v>
       </c>
-      <c r="T108" t="inlineStr">
+      <c r="T108" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U108" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z108" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6967,15 +8606,26 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr">
+      <c r="R109" s="0" t="inlineStr">
         <is>
           <t>bruno.rothbury@example.com</t>
         </is>
       </c>
-      <c r="S109" t="n">
+      <c r="S109" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T109" t="inlineStr">
+      <c r="T109" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U109" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z109" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -7010,7 +8660,11 @@
         <f>IF(F110="","",TODAY()-F110)</f>
         <v/>
       </c>
-      <c r="H110" s="11" t="n"/>
+      <c r="H110" s="11" t="inlineStr">
+        <is>
+          <t>get my side project to 100 users</t>
+        </is>
+      </c>
       <c r="I110" s="11" t="n"/>
       <c r="J110" s="11" t="n"/>
       <c r="K110" s="17" t="n">
@@ -7026,17 +8680,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr">
+      <c r="R110" s="0" t="inlineStr">
         <is>
           <t>callum.kelso@example.com</t>
         </is>
       </c>
-      <c r="S110" t="n">
+      <c r="S110" s="0" t="n">
         <v>31</v>
       </c>
-      <c r="T110" t="inlineStr">
+      <c r="T110" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U110" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="V110" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z110" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7085,17 +8755,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr">
+      <c r="R111" s="0" t="inlineStr">
         <is>
           <t>emmett.trenchard@example.com</t>
         </is>
       </c>
-      <c r="S111" t="n">
+      <c r="S111" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="T111" t="inlineStr">
+      <c r="T111" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U111" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z111" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7128,7 +8809,11 @@
         <f>IF(F112="","",TODAY()-F112)</f>
         <v/>
       </c>
-      <c r="H112" s="11" t="n"/>
+      <c r="H112" s="11" t="inlineStr">
+        <is>
+          <t>build a morning routine and keep it for 90 days</t>
+        </is>
+      </c>
       <c r="I112" s="11" t="n"/>
       <c r="J112" s="11" t="n"/>
       <c r="K112" s="17" t="n">
@@ -7144,15 +8829,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr">
+      <c r="R112" s="0" t="inlineStr">
         <is>
           <t>mateo.yardley@example.com</t>
         </is>
       </c>
-      <c r="S112" t="n">
+      <c r="S112" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T112" t="inlineStr">
+      <c r="T112" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z112" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -7187,7 +8888,11 @@
         <f>IF(F113="","",TODAY()-F113)</f>
         <v/>
       </c>
-      <c r="H113" s="11" t="n"/>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>land 3 new consulting clients</t>
+        </is>
+      </c>
       <c r="I113" s="11" t="n"/>
       <c r="J113" s="11" t="n"/>
       <c r="K113" s="17" t="n">
@@ -7203,15 +8908,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr">
+      <c r="R113" s="0" t="inlineStr">
         <is>
           <t>stanley.bramwell@example.com</t>
         </is>
       </c>
-      <c r="S113" t="n">
+      <c r="S113" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T113" t="inlineStr">
+      <c r="T113" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="W113" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z113" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -7262,17 +8983,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr">
+      <c r="R114" s="0" t="inlineStr">
         <is>
           <t>wallace.lindqvist@example.com</t>
         </is>
       </c>
-      <c r="S114" t="n">
+      <c r="S114" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="T114" t="inlineStr">
+      <c r="T114" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U114" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z114" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7321,17 +9053,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr">
+      <c r="R115" s="0" t="inlineStr">
         <is>
           <t>paolo.ingram@example.com</t>
         </is>
       </c>
-      <c r="S115" t="n">
+      <c r="S115" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="T115" t="inlineStr">
+      <c r="T115" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U115" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V115" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z115" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7380,17 +9123,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr">
+      <c r="R116" s="0" t="inlineStr">
         <is>
           <t>oscar.selwyn@example.com</t>
         </is>
       </c>
-      <c r="S116" t="n">
+      <c r="S116" s="0" t="n">
         <v>39</v>
       </c>
-      <c r="T116" t="inlineStr">
+      <c r="T116" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U116" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z116" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7439,17 +9193,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr">
+      <c r="R117" s="0" t="inlineStr">
         <is>
           <t>ivan.tavish@example.com</t>
         </is>
       </c>
-      <c r="S117" t="n">
+      <c r="S117" s="0" t="n">
         <v>34</v>
       </c>
-      <c r="T117" t="inlineStr">
+      <c r="T117" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U117" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z117" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7498,15 +9263,26 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr">
+      <c r="R118" s="0" t="inlineStr">
         <is>
           <t>declan.halewood@example.com</t>
         </is>
       </c>
-      <c r="S118" t="n">
+      <c r="S118" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T118" t="inlineStr">
+      <c r="T118" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U118" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -7557,17 +9333,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr">
+      <c r="R119" s="0" t="inlineStr">
         <is>
           <t>vernon.harrington@example.com</t>
         </is>
       </c>
-      <c r="S119" t="n">
+      <c r="S119" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="T119" t="inlineStr">
+      <c r="T119" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U119" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z119" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7600,7 +9387,11 @@
         <f>IF(F120="","",TODAY()-F120)</f>
         <v/>
       </c>
-      <c r="H120" s="11" t="n"/>
+      <c r="H120" s="11" t="inlineStr">
+        <is>
+          <t>get comfortable speaking on stage</t>
+        </is>
+      </c>
       <c r="I120" s="11" t="n"/>
       <c r="J120" s="11" t="n"/>
       <c r="K120" s="17" t="n">
@@ -7616,15 +9407,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr">
+      <c r="R120" s="0" t="inlineStr">
         <is>
           <t>leonard.rowntree@example.com</t>
         </is>
       </c>
-      <c r="S120" t="n">
+      <c r="S120" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T120" t="inlineStr">
+      <c r="T120" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U120" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="W120" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z120" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -7659,7 +9466,11 @@
         <f>IF(F121="","",TODAY()-F121)</f>
         <v/>
       </c>
-      <c r="H121" s="11" t="n"/>
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>pay off my credit card</t>
+        </is>
+      </c>
       <c r="I121" s="11" t="n"/>
       <c r="J121" s="11" t="n"/>
       <c r="K121" s="17" t="n">
@@ -7675,17 +9486,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr">
+      <c r="R121" s="0" t="inlineStr">
         <is>
           <t>alvaro.montgomery@example.com</t>
         </is>
       </c>
-      <c r="S121" t="n">
+      <c r="S121" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="T121" t="inlineStr">
+      <c r="T121" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U121" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V121" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="W121" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z121" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7734,17 +9561,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr">
+      <c r="R122" s="0" t="inlineStr">
         <is>
           <t>tomas.upton@example.com</t>
         </is>
       </c>
-      <c r="S122" t="n">
+      <c r="S122" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="T122" t="inlineStr">
+      <c r="T122" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U122" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="V122" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z122" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7777,7 +9615,11 @@
         <f>IF(F123="","",TODAY()-F123)</f>
         <v/>
       </c>
-      <c r="H123" s="11" t="n"/>
+      <c r="H123" s="11" t="inlineStr">
+        <is>
+          <t>launch a paid workshop</t>
+        </is>
+      </c>
       <c r="I123" s="11" t="n"/>
       <c r="J123" s="11" t="n"/>
       <c r="K123" s="17" t="n">
@@ -7793,15 +9635,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr">
+      <c r="R123" s="0" t="inlineStr">
         <is>
           <t>ross.fairbanks@example.com</t>
         </is>
       </c>
-      <c r="S123" t="n">
+      <c r="S123" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T123" t="inlineStr">
+      <c r="T123" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U123" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z123" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -7852,17 +9710,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr">
+      <c r="R124" s="0" t="inlineStr">
         <is>
           <t>jonah.radcliffe@example.com</t>
         </is>
       </c>
-      <c r="S124" t="n">
+      <c r="S124" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="T124" t="inlineStr">
+      <c r="T124" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U124" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V124" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z124" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7911,15 +9780,26 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr">
+      <c r="R125" s="0" t="inlineStr">
         <is>
           <t>ivan.winterbourne@example.com</t>
         </is>
       </c>
-      <c r="S125" t="n">
+      <c r="S125" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T125" t="inlineStr">
+      <c r="T125" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U125" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z125" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -7970,17 +9850,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr">
+      <c r="R126" s="0" t="inlineStr">
         <is>
           <t>diego.northgate@example.com</t>
         </is>
       </c>
-      <c r="S126" t="n">
+      <c r="S126" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="T126" t="inlineStr">
+      <c r="T126" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U126" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="V126" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z126" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8013,7 +9904,11 @@
         <f>IF(F127="","",TODAY()-F127)</f>
         <v/>
       </c>
-      <c r="H127" s="11" t="n"/>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>land 3 new consulting clients</t>
+        </is>
+      </c>
       <c r="I127" s="11" t="n"/>
       <c r="J127" s="11" t="n"/>
       <c r="K127" s="17" t="n">
@@ -8029,15 +9924,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr">
+      <c r="R127" s="0" t="inlineStr">
         <is>
           <t>karl.ashcombe@example.com</t>
         </is>
       </c>
-      <c r="S127" t="n">
+      <c r="S127" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T127" t="inlineStr">
+      <c r="T127" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U127" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="W127" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z127" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -8088,15 +9999,26 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr">
+      <c r="R128" s="0" t="inlineStr">
         <is>
           <t>simon.pemberton@example.com</t>
         </is>
       </c>
-      <c r="S128" t="n">
+      <c r="S128" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T128" t="inlineStr">
+      <c r="T128" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U128" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -8131,7 +10053,11 @@
         <f>IF(F129="","",TODAY()-F129)</f>
         <v/>
       </c>
-      <c r="H129" s="11" t="n"/>
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>land 3 new consulting clients</t>
+        </is>
+      </c>
       <c r="I129" s="11" t="n"/>
       <c r="J129" s="11" t="n"/>
       <c r="K129" s="17" t="n">
@@ -8147,17 +10073,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr">
+      <c r="R129" s="0" t="inlineStr">
         <is>
           <t>marcus.selwyn@example.com</t>
         </is>
       </c>
-      <c r="S129" t="n">
+      <c r="S129" s="0" t="n">
         <v>37</v>
       </c>
-      <c r="T129" t="inlineStr">
+      <c r="T129" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U129" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="W129" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z129" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8206,17 +10148,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr">
+      <c r="R130" s="0" t="inlineStr">
         <is>
           <t>martin.draper@example.com</t>
         </is>
       </c>
-      <c r="S130" t="n">
+      <c r="S130" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="T130" t="inlineStr">
+      <c r="T130" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U130" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8265,17 +10218,38 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr">
+      <c r="R131" s="0" t="inlineStr">
         <is>
           <t>raymond.jamison@example.com</t>
         </is>
       </c>
-      <c r="S131" t="n">
+      <c r="S131" s="0" t="n">
         <v>29</v>
       </c>
-      <c r="T131" t="inlineStr">
+      <c r="T131" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X131" s="0" t="inlineStr">
+        <is>
+          <t>launched the beta</t>
+        </is>
+      </c>
+      <c r="Y131" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z131" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8324,17 +10298,38 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr">
+      <c r="R132" s="0" t="inlineStr">
         <is>
           <t>vernon.hollingsworth@example.com</t>
         </is>
       </c>
-      <c r="S132" t="n">
+      <c r="S132" s="0" t="n">
         <v>34</v>
       </c>
-      <c r="T132" t="inlineStr">
+      <c r="T132" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U132" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V132" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="X132" s="0" t="inlineStr">
+        <is>
+          <t>finished chapter 3</t>
+        </is>
+      </c>
+      <c r="Y132" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z132" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8367,7 +10362,11 @@
         <f>IF(F133="","",TODAY()-F133)</f>
         <v/>
       </c>
-      <c r="H133" s="11" t="n"/>
+      <c r="H133" s="11" t="inlineStr">
+        <is>
+          <t>launch a paid workshop</t>
+        </is>
+      </c>
       <c r="I133" s="11" t="n"/>
       <c r="J133" s="11" t="n"/>
       <c r="K133" s="17" t="n">
@@ -8383,17 +10382,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr">
+      <c r="R133" s="0" t="inlineStr">
         <is>
           <t>caleb.pemberton@example.com</t>
         </is>
       </c>
-      <c r="S133" t="n">
+      <c r="S133" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="T133" t="inlineStr">
+      <c r="T133" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U133" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V133" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z133" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8442,17 +10457,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr">
+      <c r="R134" s="0" t="inlineStr">
         <is>
           <t>cedric.zeigler@example.com</t>
         </is>
       </c>
-      <c r="S134" t="n">
+      <c r="S134" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="T134" t="inlineStr">
+      <c r="T134" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8501,17 +10527,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr">
+      <c r="R135" s="0" t="inlineStr">
         <is>
           <t>hugo.clayborne@example.com</t>
         </is>
       </c>
-      <c r="S135" t="n">
+      <c r="S135" s="0" t="n">
         <v>23</v>
       </c>
-      <c r="T135" t="inlineStr">
+      <c r="T135" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U135" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8560,17 +10597,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr">
+      <c r="R136" s="0" t="inlineStr">
         <is>
           <t>ulysses.hollingsworth@example.com</t>
         </is>
       </c>
-      <c r="S136" t="n">
+      <c r="S136" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="T136" t="inlineStr">
+      <c r="T136" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U136" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="V136" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8619,17 +10667,38 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr">
+      <c r="R137" s="0" t="inlineStr">
         <is>
           <t>wallace.pruitt@example.com</t>
         </is>
       </c>
-      <c r="S137" t="n">
+      <c r="S137" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="T137" t="inlineStr">
+      <c r="T137" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U137" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="V137" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X137" s="0" t="inlineStr">
+        <is>
+          <t>booked a podcast guest spot</t>
+        </is>
+      </c>
+      <c r="Y137" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z137" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8682,15 +10751,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr">
+      <c r="R138" s="0" t="inlineStr">
         <is>
           <t>andrei.upshaw@example.com</t>
         </is>
       </c>
-      <c r="S138" t="n">
+      <c r="S138" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T138" t="inlineStr">
+      <c r="T138" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U138" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z138" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -8725,7 +10810,11 @@
         <f>IF(F139="","",TODAY()-F139)</f>
         <v/>
       </c>
-      <c r="H139" s="11" t="n"/>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>finish my certification</t>
+        </is>
+      </c>
       <c r="I139" s="11" t="n"/>
       <c r="J139" s="11" t="n"/>
       <c r="K139" s="17" t="n">
@@ -8741,17 +10830,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr">
+      <c r="R139" s="0" t="inlineStr">
         <is>
           <t>gavin.ellsworth@example.com</t>
         </is>
       </c>
-      <c r="S139" t="n">
+      <c r="S139" s="0" t="n">
         <v>31</v>
       </c>
-      <c r="T139" t="inlineStr">
+      <c r="T139" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U139" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V139" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z139" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8800,15 +10905,26 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr">
+      <c r="R140" s="0" t="inlineStr">
         <is>
           <t>caleb.islington@example.com</t>
         </is>
       </c>
-      <c r="S140" t="n">
+      <c r="S140" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T140" t="inlineStr">
+      <c r="T140" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U140" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -8843,7 +10959,11 @@
         <f>IF(F141="","",TODAY()-F141)</f>
         <v/>
       </c>
-      <c r="H141" s="11" t="n"/>
+      <c r="H141" s="11" t="inlineStr">
+        <is>
+          <t>start a weekly newsletter</t>
+        </is>
+      </c>
       <c r="I141" s="11" t="n"/>
       <c r="J141" s="11" t="n"/>
       <c r="K141" s="17" t="n">
@@ -8859,17 +10979,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr">
+      <c r="R141" s="0" t="inlineStr">
         <is>
           <t>erik.ostrander@example.com</t>
         </is>
       </c>
-      <c r="S141" t="n">
+      <c r="S141" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="T141" t="inlineStr">
+      <c r="T141" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U141" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V141" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="W141" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z141" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8918,17 +11054,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr">
+      <c r="R142" s="0" t="inlineStr">
         <is>
           <t>luca.upton@example.com</t>
         </is>
       </c>
-      <c r="S142" t="n">
+      <c r="S142" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="T142" t="inlineStr">
+      <c r="T142" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U142" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V142" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z142" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8977,15 +11124,26 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R143" t="inlineStr">
+      <c r="R143" s="0" t="inlineStr">
         <is>
           <t>ivan.hollowell@example.com</t>
         </is>
       </c>
-      <c r="S143" t="n">
+      <c r="S143" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T143" t="inlineStr">
+      <c r="T143" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U143" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z143" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -9036,17 +11194,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R144" t="inlineStr">
+      <c r="R144" s="0" t="inlineStr">
         <is>
           <t>archer.nesbitt@example.com</t>
         </is>
       </c>
-      <c r="S144" t="n">
+      <c r="S144" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="T144" t="inlineStr">
+      <c r="T144" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U144" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z144" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9095,17 +11264,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R145" t="inlineStr">
+      <c r="R145" s="0" t="inlineStr">
         <is>
           <t>henrik.harrington@example.com</t>
         </is>
       </c>
-      <c r="S145" t="n">
+      <c r="S145" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="T145" t="inlineStr">
+      <c r="T145" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U145" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z145" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9138,7 +11318,11 @@
         <f>IF(F146="","",TODAY()-F146)</f>
         <v/>
       </c>
-      <c r="H146" s="11" t="n"/>
+      <c r="H146" s="11" t="inlineStr">
+        <is>
+          <t>hire a part-time assistant</t>
+        </is>
+      </c>
       <c r="I146" s="11" t="n"/>
       <c r="J146" s="11" t="n"/>
       <c r="K146" s="17" t="n">
@@ -9154,17 +11338,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R146" t="inlineStr">
+      <c r="R146" s="0" t="inlineStr">
         <is>
           <t>quentin.stanton@example.com</t>
         </is>
       </c>
-      <c r="S146" t="n">
+      <c r="S146" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="T146" t="inlineStr">
+      <c r="T146" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U146" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V146" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="W146" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z146" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9213,17 +11413,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R147" t="inlineStr">
+      <c r="R147" s="0" t="inlineStr">
         <is>
           <t>grant.grimshaw@example.com</t>
         </is>
       </c>
-      <c r="S147" t="n">
+      <c r="S147" s="0" t="n">
         <v>23</v>
       </c>
-      <c r="T147" t="inlineStr">
+      <c r="T147" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U147" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V147" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z147" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9256,7 +11467,11 @@
         <f>IF(F148="","",TODAY()-F148)</f>
         <v/>
       </c>
-      <c r="H148" s="11" t="n"/>
+      <c r="H148" s="11" t="inlineStr">
+        <is>
+          <t>move from freelance to a full-time role</t>
+        </is>
+      </c>
       <c r="I148" s="11" t="n"/>
       <c r="J148" s="11" t="n"/>
       <c r="K148" s="17" t="n">
@@ -9272,17 +11487,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R148" t="inlineStr">
+      <c r="R148" s="0" t="inlineStr">
         <is>
           <t>harold.zabriskie@example.com</t>
         </is>
       </c>
-      <c r="S148" t="n">
+      <c r="S148" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="T148" t="inlineStr">
+      <c r="T148" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U148" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="W148" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z148" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9331,17 +11562,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr">
+      <c r="R149" s="0" t="inlineStr">
         <is>
           <t>wallace.lockhart@example.com</t>
         </is>
       </c>
-      <c r="S149" t="n">
+      <c r="S149" s="0" t="n">
         <v>31</v>
       </c>
-      <c r="T149" t="inlineStr">
+      <c r="T149" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U149" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V149" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z149" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9374,7 +11616,11 @@
         <f>IF(F150="","",TODAY()-F150)</f>
         <v/>
       </c>
-      <c r="H150" s="11" t="n"/>
+      <c r="H150" s="11" t="inlineStr">
+        <is>
+          <t>land 3 new consulting clients</t>
+        </is>
+      </c>
       <c r="I150" s="11" t="n"/>
       <c r="J150" s="11" t="n"/>
       <c r="K150" s="17" t="n">
@@ -9390,17 +11636,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R150" t="inlineStr">
+      <c r="R150" s="0" t="inlineStr">
         <is>
           <t>callum.tavish@example.com</t>
         </is>
       </c>
-      <c r="S150" t="n">
+      <c r="S150" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="T150" t="inlineStr">
+      <c r="T150" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U150" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z150" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9449,17 +11711,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R151" t="inlineStr">
+      <c r="R151" s="0" t="inlineStr">
         <is>
           <t>hamish.dunhill@example.com</t>
         </is>
       </c>
-      <c r="S151" t="n">
+      <c r="S151" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="T151" t="inlineStr">
+      <c r="T151" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U151" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="V151" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z151" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9512,17 +11785,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R152" t="inlineStr">
+      <c r="R152" s="0" t="inlineStr">
         <is>
           <t>luigi.osborne@example.com</t>
         </is>
       </c>
-      <c r="S152" t="n">
+      <c r="S152" s="0" t="n">
         <v>32</v>
       </c>
-      <c r="T152" t="inlineStr">
+      <c r="T152" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U152" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V152" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="W152" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z152" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9555,7 +11844,11 @@
         <f>IF(F153="","",TODAY()-F153)</f>
         <v/>
       </c>
-      <c r="H153" s="11" t="n"/>
+      <c r="H153" s="11" t="inlineStr">
+        <is>
+          <t>raise my prices with existing clients</t>
+        </is>
+      </c>
       <c r="I153" s="11" t="n"/>
       <c r="J153" s="11" t="n"/>
       <c r="K153" s="17" t="n">
@@ -9571,17 +11864,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R153" t="inlineStr">
+      <c r="R153" s="0" t="inlineStr">
         <is>
           <t>nathan.lindqvist@example.com</t>
         </is>
       </c>
-      <c r="S153" t="n">
+      <c r="S153" s="0" t="n">
         <v>37</v>
       </c>
-      <c r="T153" t="inlineStr">
+      <c r="T153" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U153" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z153" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9627,15 +11936,26 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R154" t="inlineStr">
+      <c r="R154" s="0" t="inlineStr">
         <is>
           <t>mateo.fenwick@example.com</t>
         </is>
       </c>
-      <c r="S154" t="n">
+      <c r="S154" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T154" t="inlineStr">
+      <c r="T154" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U154" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V154" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z154" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -9683,17 +12003,28 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R155" t="inlineStr">
+      <c r="R155" s="0" t="inlineStr">
         <is>
           <t>simon.yarrow@example.com</t>
         </is>
       </c>
-      <c r="S155" t="n">
+      <c r="S155" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="T155" t="inlineStr">
+      <c r="T155" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U155" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V155" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z155" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9726,6 +12057,11 @@
         <f>IF(F156="","",TODAY()-F156)</f>
         <v/>
       </c>
+      <c r="H156" s="0" t="inlineStr">
+        <is>
+          <t>record 10 podcast episodes</t>
+        </is>
+      </c>
       <c r="K156" s="17" t="n">
         <v>46311</v>
       </c>
@@ -9739,17 +12075,33 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R156" t="inlineStr">
+      <c r="R156" s="0" t="inlineStr">
         <is>
           <t>milan.upshaw@example.com</t>
         </is>
       </c>
-      <c r="S156" t="n">
+      <c r="S156" s="0" t="n">
         <v>39</v>
       </c>
-      <c r="T156" t="inlineStr">
+      <c r="T156" s="0" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="U156" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V156" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="W156" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z156" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9782,6 +12134,11 @@
         <f>IF(F157="","",TODAY()-F157)</f>
         <v/>
       </c>
+      <c r="H157" s="0" t="inlineStr">
+        <is>
+          <t>finish the first draft of my book</t>
+        </is>
+      </c>
       <c r="K157" s="17" t="n">
         <v>46311</v>
       </c>
@@ -9795,15 +12152,31 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R157" t="inlineStr">
+      <c r="R157" s="0" t="inlineStr">
         <is>
           <t>terrence.prescott@example.com</t>
         </is>
       </c>
-      <c r="S157" t="n">
+      <c r="S157" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T157" t="inlineStr">
+      <c r="T157" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U157" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="W157" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z157" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -9827,15 +12200,15 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R158" t="inlineStr">
+      <c r="R158" s="0" t="inlineStr">
         <is>
           <t>nathaniel.pomeroy@example.com</t>
         </is>
       </c>
-      <c r="S158" t="n">
+      <c r="S158" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="T158" t="inlineStr">
+      <c r="T158" s="0" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -9898,10 +12271,21 @@
           <t>&lt;your profile link in the test community&gt;</t>
         </is>
       </c>
-      <c r="S159" t="n">
+      <c r="S159" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="T159" t="inlineStr">
+      <c r="T159" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U159" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V159" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z159" s="0" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -13275,6 +15659,87 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>review_minutes</t>
+        </is>
+      </c>
+      <c r="C1" s="19" t="inlineStr">
+        <is>
+          <t>baseline_minutes</t>
+        </is>
+      </c>
+      <c r="D1" s="19" t="inlineStr">
+        <is>
+          <t>drafts</t>
+        </is>
+      </c>
+      <c r="E1" s="19" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F1" s="19" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="G1" s="19" t="inlineStr">
+        <is>
+          <t>contacted_moved_up</t>
+        </is>
+      </c>
+      <c r="H1" s="19" t="inlineStr">
+        <is>
+          <t>contacted_total</t>
+        </is>
+      </c>
+      <c r="I1" s="19" t="inlineStr">
+        <is>
+          <t>holdout_moved_up</t>
+        </is>
+      </c>
+      <c r="J1" s="19" t="inlineStr">
+        <is>
+          <t>holdout_total</t>
+        </is>
+      </c>
+      <c r="K1" s="19" t="inlineStr">
+        <is>
+          <t>revenue_attributed</t>
+        </is>
+      </c>
+      <c r="L1" s="19" t="inlineStr">
+        <is>
+          <t>revenue_target</t>
+        </is>
+      </c>
+      <c r="M1" s="19" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -13326,6 +15791,483 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="18" min="1" max="1"/>
+    <col width="9" customWidth="1" style="18" min="2" max="2"/>
+    <col width="9" customWidth="1" style="18" min="3" max="3"/>
+    <col width="44" customWidth="1" style="18" min="4" max="4"/>
+    <col width="60" customWidth="1" style="18" min="5" max="5"/>
+    <col width="46" customWidth="1" style="18" min="6" max="6"/>
+    <col width="46" customWidth="1" style="18" min="7" max="7"/>
+    <col width="11" customWidth="1" style="18" min="8" max="8"/>
+    <col width="12" customWidth="1" style="18" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>segment</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="C1" s="19" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="D1" s="19" t="inlineStr">
+        <is>
+          <t>signal</t>
+        </is>
+      </c>
+      <c r="E1" s="19" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="F1" s="19" t="inlineStr">
+        <is>
+          <t>example_subject</t>
+        </is>
+      </c>
+      <c r="G1" s="19" t="inlineStr">
+        <is>
+          <t>voice_note_idea</t>
+        </is>
+      </c>
+      <c r="H1" s="19" t="inlineStr">
+        <is>
+          <t>added_by</t>
+        </is>
+      </c>
+      <c r="I1" s="19" t="inlineStr">
+        <is>
+          <t>added_on</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>renewal_at_risk</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Renewal within 30 days, not active for 7+ days</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>Remind them what they came for and what's coming up before renewal; one easy question</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>Before your renewal: what you said you wanted from this</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>Owner: one sentence on what they hoped to get out of the group</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>never_started</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Joined 7+ days ago, no intro, no posts</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>Lower the bar: invite a one-line intro, or to just listen in on the next call</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>No intro needed. Just come say hi</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>Owner: a personal welcome by name</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>went_quiet</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Not active for 14+ days</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Reference their goal or last contribution; ask how it's going, no guilt</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>How's the book coming along?</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>Owner: asks about their goal in their own words</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>fading</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>5+ posts in total, but no posts and no calls in 30 days</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Notice the change kindly; offer one small way back in</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>We've missed your updates</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>Owner: what they appreciated about the member's past posts</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>recent_win</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>A win logged in the last 14 days</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>Celebrate it; invite them to share how they did it with the group</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>Saw your win. Would you share how you did it?</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>Owner: congratulations, in their own words</t>
+        </is>
+      </c>
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>goal_stalled</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Goal set, not updated for 30+ days</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Check in on the goal itself; offer to reset or shrink it</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>Is the goal still the goal?</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>Owner: permission to change the goal</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>lurker</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Active in the last 7 days, but no posts and no calls in 30 days</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Turn reading into one small action: a question to answer, a thread to join</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>A quick question I think you'd answer well</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>Owner: asks them the question directly</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>skipping_calls</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Active, but no calls attended in 30 days</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Share what they missed and one reason to join the next one</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>What you missed on Thursday's call</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>Owner: the one takeaway from the last call</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>win_back</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Cancelled (export includes it)</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Warm, no-pressure note; ask what would have helped</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>No pitch. Just a question</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>Owner: thanks them for the time they were in</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16851,7 +19793,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22129,13 +25071,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="130" customWidth="1" style="18" min="1" max="1"/>
@@ -22230,9 +25172,23 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>email, posts, intro_posted: from the member export. Emails here are fictional (example.com). posts = 0 and intro_posted = no means the member never got started.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>posts_30d, calls_attended_30d, goal_updated, recent_win, recent_win_date, cancelled: fictional activity used by the segments. Real exports may not have all of them; segments that need a missing column are skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>Segments &amp; strategies: the playbook Fo follows. Edit it, switch rows off, or add rows; Fo adds rows only after you approve them in brainstorm mode.</t>
         </is>
       </c>
     </row>
@@ -23222,7 +26178,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23245,72 +26201,6 @@
       <c r="C1" s="19" t="inlineStr">
         <is>
           <t>stage</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>draft_id</t>
-        </is>
-      </c>
-      <c r="B1" s="19" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C1" s="19" t="inlineStr">
-        <is>
-          <t>member_id</t>
-        </is>
-      </c>
-      <c r="D1" s="19" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="E1" s="19" t="inlineStr">
-        <is>
-          <t>rule</t>
-        </is>
-      </c>
-      <c r="F1" s="19" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="G1" s="19" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="H1" s="19" t="inlineStr">
-        <is>
-          <t>final_text</t>
-        </is>
-      </c>
-      <c r="I1" s="19" t="inlineStr">
-        <is>
-          <t>approved_at</t>
-        </is>
-      </c>
-      <c r="J1" s="19" t="inlineStr">
-        <is>
-          <t>sent_at</t>
         </is>
       </c>
     </row>
@@ -23325,28 +26215,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
+          <t>draft_id</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="19" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>member_id</t>
         </is>
       </c>
-      <c r="C1" s="19" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
       <c r="D1" s="19" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" s="19" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="F1" s="19" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="G1" s="19" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="H1" s="19" t="inlineStr">
+        <is>
+          <t>final_text</t>
+        </is>
+      </c>
+      <c r="I1" s="19" t="inlineStr">
+        <is>
+          <t>approved_at</t>
+        </is>
+      </c>
+      <c r="J1" s="19" t="inlineStr">
+        <is>
+          <t>sent_at</t>
         </is>
       </c>
     </row>
@@ -23361,7 +26281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23372,22 +26292,17 @@
       </c>
       <c r="B1" s="19" t="inlineStr">
         <is>
-          <t>draft_id</t>
+          <t>member_id</t>
         </is>
       </c>
       <c r="C1" s="19" t="inlineStr">
         <is>
-          <t>member_id</t>
+          <t>type</t>
         </is>
       </c>
       <c r="D1" s="19" t="inlineStr">
         <is>
-          <t>flag</t>
-        </is>
-      </c>
-      <c r="E1" s="19" t="inlineStr">
-        <is>
-          <t>reason</t>
+          <t>value</t>
         </is>
       </c>
     </row>
@@ -23402,7 +26317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23413,62 +26328,22 @@
       </c>
       <c r="B1" s="19" t="inlineStr">
         <is>
-          <t>review_minutes</t>
+          <t>draft_id</t>
         </is>
       </c>
       <c r="C1" s="19" t="inlineStr">
         <is>
-          <t>baseline_minutes</t>
+          <t>member_id</t>
         </is>
       </c>
       <c r="D1" s="19" t="inlineStr">
         <is>
-          <t>drafts</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="E1" s="19" t="inlineStr">
         <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F1" s="19" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="G1" s="19" t="inlineStr">
-        <is>
-          <t>contacted_moved_up</t>
-        </is>
-      </c>
-      <c r="H1" s="19" t="inlineStr">
-        <is>
-          <t>contacted_total</t>
-        </is>
-      </c>
-      <c r="I1" s="19" t="inlineStr">
-        <is>
-          <t>holdout_moved_up</t>
-        </is>
-      </c>
-      <c r="J1" s="19" t="inlineStr">
-        <is>
-          <t>holdout_total</t>
-        </is>
-      </c>
-      <c r="K1" s="19" t="inlineStr">
-        <is>
-          <t>revenue_attributed</t>
-        </is>
-      </c>
-      <c r="L1" s="19" t="inlineStr">
-        <is>
-          <t>revenue_target</t>
-        </is>
-      </c>
-      <c r="M1" s="19" t="inlineStr">
-        <is>
-          <t>note</t>
+          <t>reason</t>
         </is>
       </c>
     </row>
